--- a/GearSage-client/pkgGear/data_raw/daiwa_lure_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_lure_import.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:N118"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -444,13 +444,16 @@
       <c r="M1" t="str">
         <v>updated_at</v>
       </c>
+      <c r="N1" t="str">
+        <v>description</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>DL1000</v>
       </c>
-      <c r="B2" t="str">
-        <v/>
+      <c r="B2">
+        <v>2</v>
       </c>
       <c r="C2" t="str">
         <v>ハンクルミノー -スティーズカスタム-HMKL MINNOW - STEEZ CUSTOM -</v>
@@ -483,6 +486,9 @@
         <v/>
       </c>
       <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
         <v/>
       </c>
     </row>
@@ -490,8 +496,8 @@
       <c r="A3" t="str">
         <v>DL1001</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
+      <c r="B3">
+        <v>2</v>
       </c>
       <c r="C3" t="str">
         <v>スティーズクランポSTEEZ CRANPO</v>
@@ -524,6 +530,9 @@
         <v/>
       </c>
       <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
         <v/>
       </c>
     </row>
@@ -531,8 +540,8 @@
       <c r="A4" t="str">
         <v>DL1002</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
+      <c r="B4">
+        <v>2</v>
       </c>
       <c r="C4" t="str">
         <v>ふく魚／ちびふく魚FUKU UO/CHIBI FUKU UO</v>
@@ -565,6 +574,9 @@
         <v/>
       </c>
       <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
         <v/>
       </c>
     </row>
@@ -572,8 +584,8 @@
       <c r="A5" t="str">
         <v>DL1003</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
+      <c r="B5">
+        <v>2</v>
       </c>
       <c r="C5" t="str">
         <v>スティーズプロップSTEEZ PROP</v>
@@ -606,6 +618,9 @@
         <v/>
       </c>
       <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
         <v/>
       </c>
     </row>
@@ -613,8 +628,8 @@
       <c r="A6" t="str">
         <v>DL1004</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
+      <c r="B6">
+        <v>2</v>
       </c>
       <c r="C6" t="str">
         <v>スティーズ スプーンSTEEZ SPOON</v>
@@ -647,6 +662,9 @@
         <v/>
       </c>
       <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
         <v/>
       </c>
     </row>
@@ -654,8 +672,8 @@
       <c r="A7" t="str">
         <v>DL1005</v>
       </c>
-      <c r="B7" t="str">
-        <v/>
+      <c r="B7">
+        <v>2</v>
       </c>
       <c r="C7" t="str">
         <v>スティーズ アプナスジョイントSTEEZ APNAS JOINT</v>
@@ -688,6 +706,9 @@
         <v/>
       </c>
       <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
         <v/>
       </c>
     </row>
@@ -695,8 +716,8 @@
       <c r="A8" t="str">
         <v>DL1006</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
+      <c r="B8">
+        <v>2</v>
       </c>
       <c r="C8" t="str">
         <v>スティーズクランクSTEEZ CRANK</v>
@@ -729,6 +750,9 @@
         <v/>
       </c>
       <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
         <v/>
       </c>
     </row>
@@ -736,8 +760,8 @@
       <c r="A9" t="str">
         <v>DL1007</v>
       </c>
-      <c r="B9" t="str">
-        <v/>
+      <c r="B9">
+        <v>2</v>
       </c>
       <c r="C9" t="str">
         <v>バンクフラッターBANK FLUTTER</v>
@@ -770,6 +794,9 @@
         <v/>
       </c>
       <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
         <v/>
       </c>
     </row>
@@ -777,8 +804,8 @@
       <c r="A10" t="str">
         <v>DL1008</v>
       </c>
-      <c r="B10" t="str">
-        <v/>
+      <c r="B10">
+        <v>2</v>
       </c>
       <c r="C10" t="str">
         <v>DジャークベイトD-JERKBAIT</v>
@@ -811,6 +838,9 @@
         <v/>
       </c>
       <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
         <v/>
       </c>
     </row>
@@ -818,8 +848,8 @@
       <c r="A11" t="str">
         <v>DL1009</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
+      <c r="B11">
+        <v>2</v>
       </c>
       <c r="C11" t="str">
         <v>スティーズ ツインバズSTEEZ TWIN BUZZ</v>
@@ -852,6 +882,9 @@
         <v/>
       </c>
       <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
         <v/>
       </c>
     </row>
@@ -859,8 +892,8 @@
       <c r="A12" t="str">
         <v>DL1010</v>
       </c>
-      <c r="B12" t="str">
-        <v/>
+      <c r="B12">
+        <v>2</v>
       </c>
       <c r="C12" t="str">
         <v>スティーズ ダブルクラッチSTEEZ DOUBLE CLUTCH</v>
@@ -893,6 +926,9 @@
         <v/>
       </c>
       <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
         <v/>
       </c>
     </row>
@@ -900,8 +936,8 @@
       <c r="A13" t="str">
         <v>DL1011</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
+      <c r="B13">
+        <v>2</v>
       </c>
       <c r="C13" t="str">
         <v>ちびふく零 / ふく零 / だいふく零CHIBI FUKU ZERO / FUKU ZERO / DAIFUKU ZERO</v>
@@ -934,6 +970,9 @@
         <v/>
       </c>
       <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
         <v/>
       </c>
     </row>
@@ -941,8 +980,8 @@
       <c r="A14" t="str">
         <v>DL1012</v>
       </c>
-      <c r="B14" t="str">
-        <v/>
+      <c r="B14">
+        <v>2</v>
       </c>
       <c r="C14" t="str">
         <v>T.D.ハイパークランクT.D.HYPER CRANK</v>
@@ -975,6 +1014,9 @@
         <v/>
       </c>
       <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
         <v/>
       </c>
     </row>
@@ -982,8 +1024,8 @@
       <c r="A15" t="str">
         <v>DL1013</v>
       </c>
-      <c r="B15" t="str">
-        <v/>
+      <c r="B15">
+        <v>2</v>
       </c>
       <c r="C15" t="str">
         <v>スティーズバズベイトSTEEZ BUZZ BAIT</v>
@@ -1016,6 +1058,9 @@
         <v/>
       </c>
       <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
         <v/>
       </c>
     </row>
@@ -1023,8 +1068,8 @@
       <c r="A16" t="str">
         <v>DL1014</v>
       </c>
-      <c r="B16" t="str">
-        <v/>
+      <c r="B16">
+        <v>2</v>
       </c>
       <c r="C16" t="str">
         <v>スティーズ ポッパーSTEEZ POPPER</v>
@@ -1057,6 +1102,9 @@
         <v/>
       </c>
       <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
         <v/>
       </c>
     </row>
@@ -1064,8 +1112,8 @@
       <c r="A17" t="str">
         <v>DL1015</v>
       </c>
-      <c r="B17" t="str">
-        <v/>
+      <c r="B17">
+        <v>2</v>
       </c>
       <c r="C17" t="str">
         <v>タイニースティーズクランクTINY STEEZ CRANK</v>
@@ -1098,6 +1146,9 @@
         <v/>
       </c>
       <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
         <v/>
       </c>
     </row>
@@ -1105,8 +1156,8 @@
       <c r="A18" t="str">
         <v>DL1016</v>
       </c>
-      <c r="B18" t="str">
-        <v/>
+      <c r="B18">
+        <v>2</v>
       </c>
       <c r="C18" t="str">
         <v>ドラウンシケーダ REV/ JrDROWN CICADA REV/ Jr</v>
@@ -1139,6 +1190,9 @@
         <v/>
       </c>
       <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
         <v/>
       </c>
     </row>
@@ -1146,8 +1200,8 @@
       <c r="A19" t="str">
         <v>DL1017</v>
       </c>
-      <c r="B19" t="str">
-        <v/>
+      <c r="B19">
+        <v>2</v>
       </c>
       <c r="C19" t="str">
         <v>T.D.ミノーT.D. MINNOW</v>
@@ -1180,6 +1234,9 @@
         <v/>
       </c>
       <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
         <v/>
       </c>
     </row>
@@ -1187,8 +1244,8 @@
       <c r="A20" t="str">
         <v>DL1018</v>
       </c>
-      <c r="B20" t="str">
-        <v/>
+      <c r="B20">
+        <v>2</v>
       </c>
       <c r="C20" t="str">
         <v>スティーズ シャッドSTEEZ SHAD</v>
@@ -1221,6 +1278,9 @@
         <v/>
       </c>
       <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
         <v/>
       </c>
     </row>
@@ -1228,8 +1288,8 @@
       <c r="A21" t="str">
         <v>DL1019</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
+      <c r="B21">
+        <v>2</v>
       </c>
       <c r="C21" t="str">
         <v>スティーズ サイレントシャッドSTEEZ SILENT SHAD</v>
@@ -1262,6 +1322,9 @@
         <v/>
       </c>
       <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
         <v/>
       </c>
     </row>
@@ -1269,8 +1332,8 @@
       <c r="A22" t="str">
         <v>DL1020</v>
       </c>
-      <c r="B22" t="str">
-        <v/>
+      <c r="B22">
+        <v>2</v>
       </c>
       <c r="C22" t="str">
         <v>スティーズスクエアSTEEZ SQUARE</v>
@@ -1303,6 +1366,9 @@
         <v/>
       </c>
       <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
         <v/>
       </c>
     </row>
@@ -1310,8 +1376,8 @@
       <c r="A23" t="str">
         <v>DL1021</v>
       </c>
-      <c r="B23" t="str">
-        <v/>
+      <c r="B23">
+        <v>2</v>
       </c>
       <c r="C23" t="str">
         <v>ドラウンドラゴンフライDROWN DRAGONFLY</v>
@@ -1344,6 +1410,9 @@
         <v/>
       </c>
       <c r="M23" t="str">
+        <v/>
+      </c>
+      <c r="N23" t="str">
         <v/>
       </c>
     </row>
@@ -1351,8 +1420,8 @@
       <c r="A24" t="str">
         <v>DL1022</v>
       </c>
-      <c r="B24" t="str">
-        <v/>
+      <c r="B24">
+        <v>2</v>
       </c>
       <c r="C24" t="str">
         <v>ふく鯰/だいふく鯰FUKU NAMAZU/DAIFUKU NAMAZU</v>
@@ -1385,6 +1454,9 @@
         <v/>
       </c>
       <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
         <v/>
       </c>
     </row>
@@ -1392,8 +1464,8 @@
       <c r="A25" t="str">
         <v>DL1023</v>
       </c>
-      <c r="B25" t="str">
-        <v/>
+      <c r="B25">
+        <v>2</v>
       </c>
       <c r="C25" t="str">
         <v>ギルネードGILLNADO</v>
@@ -1426,6 +1498,9 @@
         <v/>
       </c>
       <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
         <v/>
       </c>
     </row>
@@ -1433,8 +1508,8 @@
       <c r="A26" t="str">
         <v>DL1024</v>
       </c>
-      <c r="B26" t="str">
-        <v/>
+      <c r="B26">
+        <v>2</v>
       </c>
       <c r="C26" t="str">
         <v>ガストネードGUSTNADO</v>
@@ -1467,6 +1542,9 @@
         <v/>
       </c>
       <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
         <v/>
       </c>
     </row>
@@ -1474,8 +1552,8 @@
       <c r="A27" t="str">
         <v>DL1025</v>
       </c>
-      <c r="B27" t="str">
-        <v/>
+      <c r="B27">
+        <v>2</v>
       </c>
       <c r="C27" t="str">
         <v>スティーズ アスロックSTEEZ ASROC</v>
@@ -1508,6 +1586,9 @@
         <v/>
       </c>
       <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
         <v/>
       </c>
     </row>
@@ -1515,8 +1596,8 @@
       <c r="A28" t="str">
         <v>DL1026</v>
       </c>
-      <c r="B28" t="str">
-        <v/>
+      <c r="B28">
+        <v>2</v>
       </c>
       <c r="C28" t="str">
         <v>スティーズ スピナーベイトSTEEZ SPINNER BAIT</v>
@@ -1549,6 +1630,9 @@
         <v/>
       </c>
       <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
         <v/>
       </c>
     </row>
@@ -1556,8 +1640,8 @@
       <c r="A29" t="str">
         <v>DL1027</v>
       </c>
-      <c r="B29" t="str">
-        <v/>
+      <c r="B29">
+        <v>2</v>
       </c>
       <c r="C29" t="str">
         <v>ふく平FUKU HIRA</v>
@@ -1590,6 +1674,9 @@
         <v/>
       </c>
       <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
         <v/>
       </c>
     </row>
@@ -1597,8 +1684,8 @@
       <c r="A30" t="str">
         <v>DL1028</v>
       </c>
-      <c r="B30" t="str">
-        <v/>
+      <c r="B30">
+        <v>2</v>
       </c>
       <c r="C30" t="str">
         <v>ふく弐FUKU 2</v>
@@ -1631,6 +1718,9 @@
         <v/>
       </c>
       <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
         <v/>
       </c>
     </row>
@@ -1638,8 +1728,8 @@
       <c r="A31" t="str">
         <v>DL1029</v>
       </c>
-      <c r="B31" t="str">
-        <v/>
+      <c r="B31">
+        <v>2</v>
       </c>
       <c r="C31" t="str">
         <v>スティーズイグラSTEEZ IGLA</v>
@@ -1672,6 +1762,9 @@
         <v/>
       </c>
       <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
         <v/>
       </c>
     </row>
@@ -1679,8 +1772,8 @@
       <c r="A32" t="str">
         <v>DL1030</v>
       </c>
-      <c r="B32" t="str">
-        <v/>
+      <c r="B32">
+        <v>2</v>
       </c>
       <c r="C32" t="str">
         <v>スティーズ ペンシルSTEEZ PENCIL</v>
@@ -1713,6 +1806,9 @@
         <v/>
       </c>
       <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
         <v/>
       </c>
     </row>
@@ -1720,8 +1816,8 @@
       <c r="A33" t="str">
         <v>DL1031</v>
       </c>
-      <c r="B33" t="str">
-        <v/>
+      <c r="B33">
+        <v>2</v>
       </c>
       <c r="C33" t="str">
         <v>ちびふくシャッド弐 / ふくシャッド弐CHIBI FUKU SHAD 2 / FUKU SHAD 2</v>
@@ -1754,6 +1850,9 @@
         <v/>
       </c>
       <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
         <v/>
       </c>
     </row>
@@ -1761,8 +1860,8 @@
       <c r="A34" t="str">
         <v>DL1032</v>
       </c>
-      <c r="B34" t="str">
-        <v/>
+      <c r="B34">
+        <v>2</v>
       </c>
       <c r="C34" t="str">
         <v>スティーズ カバーチャターSTEEZ COVER CHATTER</v>
@@ -1795,6 +1894,9 @@
         <v/>
       </c>
       <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
         <v/>
       </c>
     </row>
@@ -1802,8 +1904,8 @@
       <c r="A35" t="str">
         <v>DL1033</v>
       </c>
-      <c r="B35" t="str">
-        <v/>
+      <c r="B35">
+        <v>2</v>
       </c>
       <c r="C35" t="str">
         <v>ふく壱 / ちびふく壱FUKU ICHI / CHIBI FUKU ICHI</v>
@@ -1836,6 +1938,9 @@
         <v/>
       </c>
       <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
         <v/>
       </c>
     </row>
@@ -1843,8 +1948,8 @@
       <c r="A36" t="str">
         <v>DL1034</v>
       </c>
-      <c r="B36" t="str">
-        <v/>
+      <c r="B36">
+        <v>2</v>
       </c>
       <c r="C36" t="str">
         <v>スティーズメタルバイブスリムSTEEZ METAL VIB SLIM</v>
@@ -1877,6 +1982,9 @@
         <v/>
       </c>
       <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
         <v/>
       </c>
     </row>
@@ -1884,8 +1992,8 @@
       <c r="A37" t="str">
         <v>DL1035</v>
       </c>
-      <c r="B37" t="str">
-        <v/>
+      <c r="B37">
+        <v>2</v>
       </c>
       <c r="C37" t="str">
         <v>キッケルウォーカー/キッケルウォーカー BIGKIKKER WALKER/KIKKER WALKER BIG</v>
@@ -1918,6 +2026,9 @@
         <v/>
       </c>
       <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
         <v/>
       </c>
     </row>
@@ -1925,8 +2036,8 @@
       <c r="A38" t="str">
         <v>DL1036</v>
       </c>
-      <c r="B38" t="str">
-        <v/>
+      <c r="B38">
+        <v>2</v>
       </c>
       <c r="C38" t="str">
         <v>カシューナッツCASHEW NUT</v>
@@ -1959,6 +2070,9 @@
         <v/>
       </c>
       <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
         <v/>
       </c>
     </row>
@@ -1966,8 +2080,8 @@
       <c r="A39" t="str">
         <v>DL1037</v>
       </c>
-      <c r="B39" t="str">
-        <v/>
+      <c r="B39">
+        <v>2</v>
       </c>
       <c r="C39" t="str">
         <v>T.D.バイブレーションT.D.VIBRATION</v>
@@ -2000,6 +2114,9 @@
         <v/>
       </c>
       <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
         <v/>
       </c>
     </row>
@@ -2007,8 +2124,8 @@
       <c r="A40" t="str">
         <v>DL1038</v>
       </c>
-      <c r="B40" t="str">
-        <v/>
+      <c r="B40">
+        <v>2</v>
       </c>
       <c r="C40" t="str">
         <v>ラトリンチューブキックスRATTLIN' TUBE KICKS</v>
@@ -2041,6 +2158,9 @@
         <v/>
       </c>
       <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
         <v/>
       </c>
     </row>
@@ -2048,8 +2168,8 @@
       <c r="A41" t="str">
         <v>DL1039</v>
       </c>
-      <c r="B41" t="str">
-        <v/>
+      <c r="B41">
+        <v>2</v>
       </c>
       <c r="C41" t="str">
         <v>ワイルドピーナッツ / タイニーワイルドピーナッツWILD PEANUT / TINY WILD PEANUT</v>
@@ -2082,6 +2202,9 @@
         <v/>
       </c>
       <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
         <v/>
       </c>
     </row>
@@ -2089,8 +2212,8 @@
       <c r="A42" t="str">
         <v>DL1040</v>
       </c>
-      <c r="B42" t="str">
-        <v/>
+      <c r="B42">
+        <v>2</v>
       </c>
       <c r="C42" t="str">
         <v>アーモンドALMOND</v>
@@ -2123,6 +2246,9 @@
         <v/>
       </c>
       <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
         <v/>
       </c>
     </row>
@@ -2130,8 +2256,8 @@
       <c r="A43" t="str">
         <v>DL1041</v>
       </c>
-      <c r="B43" t="str">
-        <v/>
+      <c r="B43">
+        <v>2</v>
       </c>
       <c r="C43" t="str">
         <v>スティーズ ブラーモSTEEZ BRAMO</v>
@@ -2164,6 +2290,9 @@
         <v/>
       </c>
       <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
         <v/>
       </c>
     </row>
@@ -2171,8 +2300,8 @@
       <c r="A44" t="str">
         <v>DL1042</v>
       </c>
-      <c r="B44" t="str">
-        <v/>
+      <c r="B44">
+        <v>2</v>
       </c>
       <c r="C44" t="str">
         <v>デカピーナッツ IIDEKA PEANUT II</v>
@@ -2205,6 +2334,9 @@
         <v/>
       </c>
       <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
         <v/>
       </c>
     </row>
@@ -2212,8 +2344,8 @@
       <c r="A45" t="str">
         <v>DL1043</v>
       </c>
-      <c r="B45" t="str">
-        <v/>
+      <c r="B45">
+        <v>2</v>
       </c>
       <c r="C45" t="str">
         <v>ピーナッツPEANUT</v>
@@ -2246,6 +2378,9 @@
         <v/>
       </c>
       <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
         <v/>
       </c>
     </row>
@@ -2253,8 +2388,8 @@
       <c r="A46" t="str">
         <v>DL1044</v>
       </c>
-      <c r="B46" t="str">
-        <v/>
+      <c r="B46">
+        <v>2</v>
       </c>
       <c r="C46" t="str">
         <v>スティーズバンクハッカークローSTEEZ BANK HACKER CRAW</v>
@@ -2287,6 +2422,9 @@
         <v/>
       </c>
       <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
         <v/>
       </c>
     </row>
@@ -2294,8 +2432,8 @@
       <c r="A47" t="str">
         <v>DL1045</v>
       </c>
-      <c r="B47" t="str">
-        <v/>
+      <c r="B47">
+        <v>2</v>
       </c>
       <c r="C47" t="str">
         <v>ムーブベイトMOVE BAIT</v>
@@ -2328,6 +2466,9 @@
         <v/>
       </c>
       <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
         <v/>
       </c>
     </row>
@@ -2335,8 +2476,8 @@
       <c r="A48" t="str">
         <v>DL1046</v>
       </c>
-      <c r="B48" t="str">
-        <v/>
+      <c r="B48">
+        <v>2</v>
       </c>
       <c r="C48" t="str">
         <v>タイニーピーナッツTINY PEANUT</v>
@@ -2369,6 +2510,9 @@
         <v/>
       </c>
       <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
         <v/>
       </c>
     </row>
@@ -2376,8 +2520,8 @@
       <c r="A49" t="str">
         <v>DL1047</v>
       </c>
-      <c r="B49" t="str">
-        <v/>
+      <c r="B49">
+        <v>2</v>
       </c>
       <c r="C49" t="str">
         <v>スティーズクローSTEEZ CRAW</v>
@@ -2410,6 +2554,9 @@
         <v/>
       </c>
       <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
         <v/>
       </c>
     </row>
@@ -2417,8 +2564,8 @@
       <c r="A50" t="str">
         <v>DL1048</v>
       </c>
-      <c r="B50" t="str">
-        <v/>
+      <c r="B50">
+        <v>2</v>
       </c>
       <c r="C50" t="str">
         <v>ムーブホグMOVE HOG</v>
@@ -2451,6 +2598,9 @@
         <v/>
       </c>
       <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
         <v/>
       </c>
     </row>
@@ -2458,8 +2608,8 @@
       <c r="A51" t="str">
         <v>DL1049</v>
       </c>
-      <c r="B51" t="str">
-        <v/>
+      <c r="B51">
+        <v>2</v>
       </c>
       <c r="C51" t="str">
         <v>スティーズ アプナスバグSTEEZ APNAS BUG</v>
@@ -2492,6 +2642,9 @@
         <v/>
       </c>
       <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
         <v/>
       </c>
     </row>
@@ -2499,8 +2652,8 @@
       <c r="A52" t="str">
         <v>DL1050</v>
       </c>
-      <c r="B52" t="str">
-        <v/>
+      <c r="B52">
+        <v>2</v>
       </c>
       <c r="C52" t="str">
         <v>スティーズ ポップクラッカーSTEEZ POP CRACKER</v>
@@ -2533,6 +2686,9 @@
         <v/>
       </c>
       <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
         <v/>
       </c>
     </row>
@@ -2540,8 +2696,8 @@
       <c r="A53" t="str">
         <v>DL1051</v>
       </c>
-      <c r="B53" t="str">
-        <v/>
+      <c r="B53">
+        <v>2</v>
       </c>
       <c r="C53" t="str">
         <v>スティーズ スターリングフィッシュSTEEZ STIRRING FISH</v>
@@ -2574,6 +2730,9 @@
         <v/>
       </c>
       <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
         <v/>
       </c>
     </row>
@@ -2581,8 +2740,8 @@
       <c r="A54" t="str">
         <v>DL1052</v>
       </c>
-      <c r="B54" t="str">
-        <v/>
+      <c r="B54">
+        <v>2</v>
       </c>
       <c r="C54" t="str">
         <v>シュリンピード／シュリンピードJr.SHRIMPEDE／SHRIMPEDE Jr.</v>
@@ -2615,6 +2774,9 @@
         <v/>
       </c>
       <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
         <v/>
       </c>
     </row>
@@ -2622,8 +2784,8 @@
       <c r="A55" t="str">
         <v>DL1053</v>
       </c>
-      <c r="B55" t="str">
-        <v/>
+      <c r="B55">
+        <v>2</v>
       </c>
       <c r="C55" t="str">
         <v>キッケルカーリーKIKKER CURLY</v>
@@ -2656,6 +2818,9 @@
         <v/>
       </c>
       <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
         <v/>
       </c>
     </row>
@@ -2663,8 +2828,8 @@
       <c r="A56" t="str">
         <v>DL1054</v>
       </c>
-      <c r="B56" t="str">
-        <v/>
+      <c r="B56">
+        <v>2</v>
       </c>
       <c r="C56" t="str">
         <v>スティーズネコストレートSTEEZ NEKO STRAIGHT</v>
@@ -2697,6 +2862,9 @@
         <v/>
       </c>
       <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
         <v/>
       </c>
     </row>
@@ -2704,8 +2872,8 @@
       <c r="A57" t="str">
         <v>DL1055</v>
       </c>
-      <c r="B57" t="str">
-        <v/>
+      <c r="B57">
+        <v>2</v>
       </c>
       <c r="C57" t="str">
         <v>スティーズ ホグSTEEZ HOG</v>
@@ -2738,6 +2906,9 @@
         <v/>
       </c>
       <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
         <v/>
       </c>
     </row>
@@ -2745,8 +2916,8 @@
       <c r="A58" t="str">
         <v>DL1056</v>
       </c>
-      <c r="B58" t="str">
-        <v/>
+      <c r="B58">
+        <v>2</v>
       </c>
       <c r="C58" t="str">
         <v>スティーズ パワーフィネスジグSTEEZ POWERFINESSEJIG</v>
@@ -2779,6 +2950,9 @@
         <v/>
       </c>
       <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
         <v/>
       </c>
     </row>
@@ -2786,8 +2960,8 @@
       <c r="A59" t="str">
         <v>DL1057</v>
       </c>
-      <c r="B59" t="str">
-        <v/>
+      <c r="B59">
+        <v>2</v>
       </c>
       <c r="C59" t="str">
         <v>スティーズ リアルスラッガーSTEEZ REAL SLUGGER</v>
@@ -2820,6 +2994,9 @@
         <v/>
       </c>
       <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
         <v/>
       </c>
     </row>
@@ -2827,8 +3004,8 @@
       <c r="A60" t="str">
         <v>DL1058</v>
       </c>
-      <c r="B60" t="str">
-        <v/>
+      <c r="B60">
+        <v>2</v>
       </c>
       <c r="C60" t="str">
         <v>スティーズ　ネコファットSTEEZ NEKO FAT</v>
@@ -2861,6 +3038,9 @@
         <v/>
       </c>
       <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
         <v/>
       </c>
     </row>
@@ -2868,8 +3048,8 @@
       <c r="A61" t="str">
         <v>DL1059</v>
       </c>
-      <c r="B61" t="str">
-        <v/>
+      <c r="B61">
+        <v>2</v>
       </c>
       <c r="C61" t="str">
         <v>スティーズ フィネスストレートSTEEZ FINESSE STRAIGHT</v>
@@ -2902,6 +3082,9 @@
         <v/>
       </c>
       <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
         <v/>
       </c>
     </row>
@@ -2909,8 +3092,8 @@
       <c r="A62" t="str">
         <v>DL1060</v>
       </c>
-      <c r="B62" t="str">
-        <v/>
+      <c r="B62">
+        <v>2</v>
       </c>
       <c r="C62" t="str">
         <v>スティーズネコストレートロングSTEEZ NEKO STRAIGHT LONG</v>
@@ -2943,6 +3126,9 @@
         <v/>
       </c>
       <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
         <v/>
       </c>
     </row>
@@ -2950,8 +3136,8 @@
       <c r="A63" t="str">
         <v>DL1061</v>
       </c>
-      <c r="B63" t="str">
-        <v/>
+      <c r="B63">
+        <v>2</v>
       </c>
       <c r="C63" t="str">
         <v>スティーズ スターリングツインSTEEZ STIRRING TWIN</v>
@@ -2984,6 +3170,9 @@
         <v/>
       </c>
       <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
         <v/>
       </c>
     </row>
@@ -2991,8 +3180,8 @@
       <c r="A64" t="str">
         <v>DL1062</v>
       </c>
-      <c r="B64" t="str">
-        <v/>
+      <c r="B64">
+        <v>2</v>
       </c>
       <c r="C64" t="str">
         <v>スティーズ スターリングシャッドSTEEZ STIRRING SHAD</v>
@@ -3025,6 +3214,9 @@
         <v/>
       </c>
       <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
         <v/>
       </c>
     </row>
@@ -3032,8 +3224,8 @@
       <c r="A65" t="str">
         <v>DL1063</v>
       </c>
-      <c r="B65" t="str">
-        <v/>
+      <c r="B65">
+        <v>2</v>
       </c>
       <c r="C65" t="str">
         <v>BHカバージグBH COVER JIG</v>
@@ -3066,6 +3258,9 @@
         <v/>
       </c>
       <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
         <v/>
       </c>
     </row>
@@ -3073,8 +3268,8 @@
       <c r="A66" t="str">
         <v>DL1064</v>
       </c>
-      <c r="B66" t="str">
-        <v/>
+      <c r="B66">
+        <v>2</v>
       </c>
       <c r="C66" t="str">
         <v>BHマルチジグBH MULTI JIG</v>
@@ -3107,6 +3302,9 @@
         <v/>
       </c>
       <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
         <v/>
       </c>
     </row>
@@ -3114,8 +3312,8 @@
       <c r="A67" t="str">
         <v>DL1065</v>
       </c>
-      <c r="B67" t="str">
-        <v/>
+      <c r="B67">
+        <v>2</v>
       </c>
       <c r="C67" t="str">
         <v>スティーズ パワーフィネスジグ TYPEカバーSTEEZ POWERFINESSEJIG TYPECOVER</v>
@@ -3148,6 +3346,9 @@
         <v/>
       </c>
       <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
         <v/>
       </c>
     </row>
@@ -3155,8 +3356,8 @@
       <c r="A68" t="str">
         <v>DL1066</v>
       </c>
-      <c r="B68" t="str">
-        <v/>
+      <c r="B68">
+        <v>2</v>
       </c>
       <c r="C68" t="str">
         <v>BHジグスピナーBH JIG SPINNER</v>
@@ -3189,6 +3390,9 @@
         <v/>
       </c>
       <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
         <v/>
       </c>
     </row>
@@ -3196,8 +3400,8 @@
       <c r="A69" t="str">
         <v>DL1067</v>
       </c>
-      <c r="B69" t="str">
-        <v/>
+      <c r="B69">
+        <v>2</v>
       </c>
       <c r="C69" t="str">
         <v>BHミニジグBH MINI JIG</v>
@@ -3230,6 +3434,9 @@
         <v/>
       </c>
       <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
         <v/>
       </c>
     </row>
@@ -3237,8 +3444,8 @@
       <c r="A70" t="str">
         <v>DL1068</v>
       </c>
-      <c r="B70" t="str">
-        <v/>
+      <c r="B70">
+        <v>2</v>
       </c>
       <c r="C70" t="str">
         <v>シルバークリークミノージョイントSILVER CREEK MINNOW JOINT</v>
@@ -3271,6 +3478,9 @@
         <v/>
       </c>
       <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
         <v/>
       </c>
     </row>
@@ -3278,8 +3488,8 @@
       <c r="A71" t="str">
         <v>DL1069</v>
       </c>
-      <c r="B71" t="str">
-        <v/>
+      <c r="B71">
+        <v>2</v>
       </c>
       <c r="C71" t="str">
         <v>シルバークリークミノーSILVER CREEK MINNOW</v>
@@ -3312,6 +3522,9 @@
         <v/>
       </c>
       <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
         <v/>
       </c>
     </row>
@@ -3319,8 +3532,8 @@
       <c r="A72" t="str">
         <v>DL1070</v>
       </c>
-      <c r="B72" t="str">
-        <v/>
+      <c r="B72">
+        <v>2</v>
       </c>
       <c r="C72" t="str">
         <v>BHメタルバイブBH METAL VIB</v>
@@ -3353,6 +3566,9 @@
         <v/>
       </c>
       <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
         <v/>
       </c>
     </row>
@@ -3360,8 +3576,8 @@
       <c r="A73" t="str">
         <v>DL1071</v>
       </c>
-      <c r="B73" t="str">
-        <v/>
+      <c r="B73">
+        <v>2</v>
       </c>
       <c r="C73" t="str">
         <v>ダブルクラッチF1 C&amp;R カスタムDOUBLECLUTCH F1 C&amp;R CUSTOM</v>
@@ -3394,6 +3610,9 @@
         <v/>
       </c>
       <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
         <v/>
       </c>
     </row>
@@ -3401,8 +3620,8 @@
       <c r="A74" t="str">
         <v>DL1072</v>
       </c>
-      <c r="B74" t="str">
-        <v/>
+      <c r="B74">
+        <v>2</v>
       </c>
       <c r="C74" t="str">
         <v>シルバークリークミノーTGSILVER CREEK MINNOW TG</v>
@@ -3435,6 +3654,9 @@
         <v/>
       </c>
       <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
         <v/>
       </c>
     </row>
@@ -3442,8 +3664,8 @@
       <c r="A75" t="str">
         <v>DL1073</v>
       </c>
-      <c r="B75" t="str">
-        <v/>
+      <c r="B75">
+        <v>2</v>
       </c>
       <c r="C75" t="str">
         <v>シルバークリークミノーダートカスタムSILVER CREEK MINNOW DART CUSTOM</v>
@@ -3476,6 +3698,9 @@
         <v/>
       </c>
       <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
         <v/>
       </c>
     </row>
@@ -3483,8 +3708,8 @@
       <c r="A76" t="str">
         <v>DL1074</v>
       </c>
-      <c r="B76" t="str">
-        <v/>
+      <c r="B76">
+        <v>2</v>
       </c>
       <c r="C76" t="str">
         <v>ワブクラ30DR  C&amp;R カスタムWABCRA30DR C&amp;R CUSTOM</v>
@@ -3517,6 +3742,9 @@
         <v/>
       </c>
       <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
         <v/>
       </c>
     </row>
@@ -3524,8 +3752,8 @@
       <c r="A77" t="str">
         <v>DL1075</v>
       </c>
-      <c r="B77" t="str">
-        <v/>
+      <c r="B77">
+        <v>2</v>
       </c>
       <c r="C77" t="str">
         <v>ドクターミノーIIジョイントDr.MINNOW II JOINT</v>
@@ -3558,6 +3786,9 @@
         <v/>
       </c>
       <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
         <v/>
       </c>
     </row>
@@ -3565,8 +3796,8 @@
       <c r="A78" t="str">
         <v>DL1076</v>
       </c>
-      <c r="B78" t="str">
-        <v/>
+      <c r="B78">
+        <v>2</v>
       </c>
       <c r="C78" t="str">
         <v>シルバークリークミノーダイビングカスタムSILVER CREEK MINNOW DIVING CUSTOM</v>
@@ -3599,6 +3830,9 @@
         <v/>
       </c>
       <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
         <v/>
       </c>
     </row>
@@ -3606,8 +3840,8 @@
       <c r="A79" t="str">
         <v>DL1077</v>
       </c>
-      <c r="B79" t="str">
-        <v/>
+      <c r="B79">
+        <v>2</v>
       </c>
       <c r="C79" t="str">
         <v>シルバークリークミノースローフォールカスタムSILVER CREEK MINNOW SLOW FALL CUSTOM</v>
@@ -3640,6 +3874,9 @@
         <v/>
       </c>
       <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
         <v/>
       </c>
     </row>
@@ -3647,8 +3884,8 @@
       <c r="A80" t="str">
         <v>DL1078</v>
       </c>
-      <c r="B80" t="str">
-        <v/>
+      <c r="B80">
+        <v>2</v>
       </c>
       <c r="C80" t="str">
         <v>DR.ミノー2DR. MINNOW Ⅱ</v>
@@ -3681,6 +3918,9 @@
         <v/>
       </c>
       <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
         <v/>
       </c>
     </row>
@@ -3688,8 +3928,8 @@
       <c r="A81" t="str">
         <v>DL1079</v>
       </c>
-      <c r="B81" t="str">
-        <v/>
+      <c r="B81">
+        <v>2</v>
       </c>
       <c r="C81" t="str">
         <v>チヌーク SCHINOOK S</v>
@@ -3722,6 +3962,9 @@
         <v/>
       </c>
       <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
         <v/>
       </c>
     </row>
@@ -3729,8 +3972,8 @@
       <c r="A82" t="str">
         <v>DL1080</v>
       </c>
-      <c r="B82" t="str">
-        <v/>
+      <c r="B82">
+        <v>2</v>
       </c>
       <c r="C82" t="str">
         <v>クルセイダー激アツCRUSADER GEKIATSU</v>
@@ -3763,6 +4006,9 @@
         <v/>
       </c>
       <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
         <v/>
       </c>
     </row>
@@ -3770,8 +4016,8 @@
       <c r="A83" t="str">
         <v>DL1081</v>
       </c>
-      <c r="B83" t="str">
-        <v/>
+      <c r="B83">
+        <v>2</v>
       </c>
       <c r="C83" t="str">
         <v>Dr.ミノーII エリアチューンDr.MINNOW II AREA TUNE</v>
@@ -3804,6 +4050,9 @@
         <v/>
       </c>
       <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
         <v/>
       </c>
     </row>
@@ -3811,8 +4060,8 @@
       <c r="A84" t="str">
         <v>DL1082</v>
       </c>
-      <c r="B84" t="str">
-        <v/>
+      <c r="B84">
+        <v>2</v>
       </c>
       <c r="C84" t="str">
         <v>クルセイダーCRUSADER</v>
@@ -3845,6 +4094,9 @@
         <v/>
       </c>
       <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
         <v/>
       </c>
     </row>
@@ -3852,8 +4104,8 @@
       <c r="A85" t="str">
         <v>DL1083</v>
       </c>
-      <c r="B85" t="str">
-        <v/>
+      <c r="B85">
+        <v>2</v>
       </c>
       <c r="C85" t="str">
         <v>チヌーク激アツCHINOOK GEKIATSU</v>
@@ -3886,6 +4138,9 @@
         <v/>
       </c>
       <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
         <v/>
       </c>
     </row>
@@ -3893,8 +4148,8 @@
       <c r="A86" t="str">
         <v>DL1084</v>
       </c>
-      <c r="B86" t="str">
-        <v/>
+      <c r="B86">
+        <v>2</v>
       </c>
       <c r="C86" t="str">
         <v>レーザーチヌークSLASER CHINOOK S</v>
@@ -3927,6 +4182,9 @@
         <v/>
       </c>
       <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
         <v/>
       </c>
     </row>
@@ -3934,8 +4192,8 @@
       <c r="A87" t="str">
         <v>DL1085</v>
       </c>
-      <c r="B87" t="str">
-        <v/>
+      <c r="B87">
+        <v>2</v>
       </c>
       <c r="C87" t="str">
         <v>ブレットンBRETTON</v>
@@ -3968,6 +4226,9 @@
         <v/>
       </c>
       <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
         <v/>
       </c>
     </row>
@@ -3975,8 +4236,8 @@
       <c r="A88" t="str">
         <v>DL1086</v>
       </c>
-      <c r="B88" t="str">
-        <v/>
+      <c r="B88">
+        <v>2</v>
       </c>
       <c r="C88" t="str">
         <v>SilverCreek スピナーSILVER CREEK SPINNER</v>
@@ -4009,6 +4270,9 @@
         <v/>
       </c>
       <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
         <v/>
       </c>
     </row>
@@ -4016,8 +4280,8 @@
       <c r="A89" t="str">
         <v>DL1087</v>
       </c>
-      <c r="B89" t="str">
-        <v/>
+      <c r="B89">
+        <v>2</v>
       </c>
       <c r="C89" t="str">
         <v>シルバークリーク スピナーSSSILVER CREEK SPINNER SS</v>
@@ -4050,6 +4314,9 @@
         <v/>
       </c>
       <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
         <v/>
       </c>
     </row>
@@ -4057,8 +4324,8 @@
       <c r="A90" t="str">
         <v>DL1088</v>
       </c>
-      <c r="B90" t="str">
-        <v/>
+      <c r="B90">
+        <v>2</v>
       </c>
       <c r="C90" t="str">
         <v>プレッソ ダブルクラッチ 60F1 tuned by HMKLPRESSO DOUBLECLUTCH60F1 tuned by HMKL</v>
@@ -4091,6 +4358,9 @@
         <v/>
       </c>
       <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
         <v/>
       </c>
     </row>
@@ -4098,8 +4368,8 @@
       <c r="A91" t="str">
         <v>DL1089</v>
       </c>
-      <c r="B91" t="str">
-        <v/>
+      <c r="B91">
+        <v>2</v>
       </c>
       <c r="C91" t="str">
         <v>プレッソ ダブルクラッチ 60SS tuned by HMKLPRESSO DOUBLE CLUTCH 60SS tuned by HMKL</v>
@@ -4132,6 +4402,9 @@
         <v/>
       </c>
       <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
         <v/>
       </c>
     </row>
@@ -4139,8 +4412,8 @@
       <c r="A92" t="str">
         <v>DL1090</v>
       </c>
-      <c r="B92" t="str">
-        <v/>
+      <c r="B92">
+        <v>2</v>
       </c>
       <c r="C92" t="str">
         <v>プレッソ ダブルクラッチ 45S tuned by HMKLPRESSO DOUBLE CLUTCH 45S tuned by HMKL</v>
@@ -4173,6 +4446,9 @@
         <v/>
       </c>
       <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
         <v/>
       </c>
     </row>
@@ -4180,8 +4456,8 @@
       <c r="A93" t="str">
         <v>DL1091</v>
       </c>
-      <c r="B93" t="str">
-        <v/>
+      <c r="B93">
+        <v>2</v>
       </c>
       <c r="C93" t="str">
         <v>プレッソ ダブルクラッチ 60SHF tuned by HMKLPRESSO DOUBLECLUTCH 60SHF tuned by HMKL</v>
@@ -4214,6 +4490,9 @@
         <v/>
       </c>
       <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
         <v/>
       </c>
     </row>
@@ -4221,8 +4500,8 @@
       <c r="A94" t="str">
         <v>DL1092</v>
       </c>
-      <c r="B94" t="str">
-        <v/>
+      <c r="B94">
+        <v>2</v>
       </c>
       <c r="C94" t="str">
         <v>プレッソ ダブルクラッチ 45F1 tuned by HMKLPRESSO DOUBLECLUTCH45F1 tuned by HMKL</v>
@@ -4255,6 +4534,9 @@
         <v/>
       </c>
       <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
         <v/>
       </c>
     </row>
@@ -4262,8 +4544,8 @@
       <c r="A95" t="str">
         <v>DL1093</v>
       </c>
-      <c r="B95" t="str">
-        <v/>
+      <c r="B95">
+        <v>2</v>
       </c>
       <c r="C95" t="str">
         <v>プレッソ ダブルクラッチ 75SS tuned by HMKLPRESSO DOUBLE CLUTCH 75SS tuned by HMKL</v>
@@ -4296,6 +4578,9 @@
         <v/>
       </c>
       <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
         <v/>
       </c>
     </row>
@@ -4303,8 +4588,8 @@
       <c r="A96" t="str">
         <v>DL1094</v>
       </c>
-      <c r="B96" t="str">
-        <v/>
+      <c r="B96">
+        <v>2</v>
       </c>
       <c r="C96" t="str">
         <v>プレッソ ワブクラJr.PRESSO WABCRA Jr.</v>
@@ -4337,6 +4622,9 @@
         <v/>
       </c>
       <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
         <v/>
       </c>
     </row>
@@ -4344,8 +4632,8 @@
       <c r="A97" t="str">
         <v>DL1095</v>
       </c>
-      <c r="B97" t="str">
-        <v/>
+      <c r="B97">
+        <v>2</v>
       </c>
       <c r="C97" t="str">
         <v>プレッソ ワブクラスリムPRESSO WABCRA SLIM</v>
@@ -4378,6 +4666,9 @@
         <v/>
       </c>
       <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
         <v/>
       </c>
     </row>
@@ -4385,8 +4676,8 @@
       <c r="A98" t="str">
         <v>DL1096</v>
       </c>
-      <c r="B98" t="str">
-        <v/>
+      <c r="B98">
+        <v>2</v>
       </c>
       <c r="C98" t="str">
         <v>プレッソ ダブルクラッチ 48F tuned by HMKLPRESSO DOUBLECLUTCH 48F tuned by HMKL</v>
@@ -4419,6 +4710,9 @@
         <v/>
       </c>
       <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
         <v/>
       </c>
     </row>
@@ -4426,8 +4720,8 @@
       <c r="A99" t="str">
         <v>DL1097</v>
       </c>
-      <c r="B99" t="str">
-        <v/>
+      <c r="B99">
+        <v>2</v>
       </c>
       <c r="C99" t="str">
         <v>プレッソ メガポッピンバグPRESSO MEGA POPPIN'BUG</v>
@@ -4460,6 +4754,9 @@
         <v/>
       </c>
       <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
         <v/>
       </c>
     </row>
@@ -4467,8 +4764,8 @@
       <c r="A100" t="str">
         <v>DL1098</v>
       </c>
-      <c r="B100" t="str">
-        <v/>
+      <c r="B100">
+        <v>2</v>
       </c>
       <c r="C100" t="str">
         <v>プレッソ ニョロクレイジー S/SSPRESSO NYORO CLAZY S/SS</v>
@@ -4501,6 +4798,9 @@
         <v/>
       </c>
       <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
         <v/>
       </c>
     </row>
@@ -4508,8 +4808,8 @@
       <c r="A101" t="str">
         <v>DL1099</v>
       </c>
-      <c r="B101" t="str">
-        <v/>
+      <c r="B101">
+        <v>2</v>
       </c>
       <c r="C101" t="str">
         <v>プレッソ ステップダートPRESSO STEP DART</v>
@@ -4542,6 +4842,9 @@
         <v/>
       </c>
       <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
         <v/>
       </c>
     </row>
@@ -4549,8 +4852,8 @@
       <c r="A102" t="str">
         <v>DL1100</v>
       </c>
-      <c r="B102" t="str">
-        <v/>
+      <c r="B102">
+        <v>2</v>
       </c>
       <c r="C102" t="str">
         <v>プレッソ ポッピンバグ / ラトリンポッピンバグPRESSO POPPIN'BUG / RATLLIN'POPPIN'BUG</v>
@@ -4583,6 +4886,9 @@
         <v/>
       </c>
       <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
         <v/>
       </c>
     </row>
@@ -4590,8 +4896,8 @@
       <c r="A103" t="str">
         <v>DL1101</v>
       </c>
-      <c r="B103" t="str">
-        <v/>
+      <c r="B103">
+        <v>2</v>
       </c>
       <c r="C103" t="str">
         <v>プレッソ リバクラPRESSO RIVECRA</v>
@@ -4624,6 +4930,9 @@
         <v/>
       </c>
       <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
         <v/>
       </c>
     </row>
@@ -4631,8 +4940,8 @@
       <c r="A104" t="str">
         <v>DL1102</v>
       </c>
-      <c r="B104" t="str">
-        <v/>
+      <c r="B104">
+        <v>2</v>
       </c>
       <c r="C104" t="str">
         <v>プレッソ ラトリンウェイクバグPRESSO RATLLIN'WAKE BUG</v>
@@ -4665,6 +4974,9 @@
         <v/>
       </c>
       <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
         <v/>
       </c>
     </row>
@@ -4672,8 +4984,8 @@
       <c r="A105" t="str">
         <v>DL1103</v>
       </c>
-      <c r="B105" t="str">
-        <v/>
+      <c r="B105">
+        <v>2</v>
       </c>
       <c r="C105" t="str">
         <v>ドクターミノー ジョイント 5F プレッソチューンDR. MINNOW JOINT 5F PRESSO TUNE</v>
@@ -4706,6 +5018,9 @@
         <v/>
       </c>
       <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
         <v/>
       </c>
     </row>
@@ -4713,8 +5028,8 @@
       <c r="A106" t="str">
         <v>DL1104</v>
       </c>
-      <c r="B106" t="str">
-        <v/>
+      <c r="B106">
+        <v>2</v>
       </c>
       <c r="C106" t="str">
         <v>プレッソ ワブクラPRESSO WABCRA</v>
@@ -4747,6 +5062,9 @@
         <v/>
       </c>
       <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
         <v/>
       </c>
     </row>
@@ -4754,8 +5072,8 @@
       <c r="A107" t="str">
         <v>DL1105</v>
       </c>
-      <c r="B107" t="str">
-        <v/>
+      <c r="B107">
+        <v>2</v>
       </c>
       <c r="C107" t="str">
         <v>鱒ノ芋虫MASUNO IMOMUSHI</v>
@@ -4788,6 +5106,9 @@
         <v/>
       </c>
       <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
         <v/>
       </c>
     </row>
@@ -4795,8 +5116,8 @@
       <c r="A108" t="str">
         <v>DL1106</v>
       </c>
-      <c r="B108" t="str">
-        <v/>
+      <c r="B108">
+        <v>2</v>
       </c>
       <c r="C108" t="str">
         <v>プレッソ ディーザPRESSO DEAZA</v>
@@ -4829,6 +5150,9 @@
         <v/>
       </c>
       <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
         <v/>
       </c>
     </row>
@@ -4836,8 +5160,8 @@
       <c r="A109" t="str">
         <v>DL1107</v>
       </c>
-      <c r="B109" t="str">
-        <v/>
+      <c r="B109">
+        <v>2</v>
       </c>
       <c r="C109" t="str">
         <v>鱒ノ小魚MASUNO KOZAKAN</v>
@@ -4870,6 +5194,9 @@
         <v/>
       </c>
       <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
         <v/>
       </c>
     </row>
@@ -4877,8 +5204,8 @@
       <c r="A110" t="str">
         <v>DL1108</v>
       </c>
-      <c r="B110" t="str">
-        <v/>
+      <c r="B110">
+        <v>2</v>
       </c>
       <c r="C110" t="str">
         <v>鱒の小枝 スクリューMASU NO KOEDA SCREW</v>
@@ -4911,6 +5238,9 @@
         <v/>
       </c>
       <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
         <v/>
       </c>
     </row>
@@ -4918,8 +5248,8 @@
       <c r="A111" t="str">
         <v>DL1109</v>
       </c>
-      <c r="B111" t="str">
-        <v/>
+      <c r="B111">
+        <v>2</v>
       </c>
       <c r="C111" t="str">
         <v>鱒ノつぼみMASU NO TSUBOMI</v>
@@ -4952,6 +5282,9 @@
         <v/>
       </c>
       <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
         <v/>
       </c>
     </row>
@@ -4959,8 +5292,8 @@
       <c r="A112" t="str">
         <v>DL1110</v>
       </c>
-      <c r="B112" t="str">
-        <v/>
+      <c r="B112">
+        <v>2</v>
       </c>
       <c r="C112" t="str">
         <v>鱒ノ筒／鱒ノ筒Jr.MASU NO TSUTSU／MASU NO TSUTSU Jr.</v>
@@ -4993,6 +5326,9 @@
         <v/>
       </c>
       <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
         <v/>
       </c>
     </row>
@@ -5000,8 +5336,8 @@
       <c r="A113" t="str">
         <v>DL1111</v>
       </c>
-      <c r="B113" t="str">
-        <v/>
+      <c r="B113">
+        <v>2</v>
       </c>
       <c r="C113" t="str">
         <v>鱒ノ種MASUNOTANE</v>
@@ -5034,6 +5370,9 @@
         <v/>
       </c>
       <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
         <v/>
       </c>
     </row>
@@ -5041,8 +5380,8 @@
       <c r="A114" t="str">
         <v>DL1112</v>
       </c>
-      <c r="B114" t="str">
-        <v/>
+      <c r="B114">
+        <v>2</v>
       </c>
       <c r="C114" t="str">
         <v>鱒もろこしMASUMOROKOSHI</v>
@@ -5075,6 +5414,9 @@
         <v/>
       </c>
       <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114" t="str">
         <v/>
       </c>
     </row>
@@ -5082,8 +5424,8 @@
       <c r="A115" t="str">
         <v>DL1113</v>
       </c>
-      <c r="B115" t="str">
-        <v/>
+      <c r="B115">
+        <v>2</v>
       </c>
       <c r="C115" t="str">
         <v>鱒ノ小枝／鱒ノ小枝Jr.MASUNOKOEDA／MASUNOKOEDA Jr.</v>
@@ -5116,6 +5458,9 @@
         <v/>
       </c>
       <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
         <v/>
       </c>
     </row>
@@ -5123,8 +5468,8 @@
       <c r="A116" t="str">
         <v>DL1114</v>
       </c>
-      <c r="B116" t="str">
-        <v/>
+      <c r="B116">
+        <v>2</v>
       </c>
       <c r="C116" t="str">
         <v>プレッソ アトラPRESSO ATTRA</v>
@@ -5157,6 +5502,9 @@
         <v/>
       </c>
       <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116" t="str">
         <v/>
       </c>
     </row>
@@ -5164,8 +5512,8 @@
       <c r="A117" t="str">
         <v>DL1115</v>
       </c>
-      <c r="B117" t="str">
-        <v/>
+      <c r="B117">
+        <v>2</v>
       </c>
       <c r="C117" t="str">
         <v>プレッソ イヴ激アツ 2.5PRESSO EVE GEKIATSU 2.5</v>
@@ -5198,6 +5546,9 @@
         <v/>
       </c>
       <c r="M117" t="str">
+        <v/>
+      </c>
+      <c r="N117" t="str">
         <v/>
       </c>
     </row>
@@ -5205,8 +5556,8 @@
       <c r="A118" t="str">
         <v>DL1116</v>
       </c>
-      <c r="B118" t="str">
-        <v/>
+      <c r="B118">
+        <v>2</v>
       </c>
       <c r="C118" t="str">
         <v>プレッソ ルミオンPRESSO LUMION</v>
@@ -5241,10 +5592,13 @@
       <c r="M118" t="str">
         <v/>
       </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M118"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N118"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/GearSage-client/pkgGear/data_raw/daiwa_lure_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_lure_import.xlsx
@@ -5605,7 +5605,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1058"/>
+  <dimension ref="A1:Q1058"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5647,6 +5647,18 @@
       <c r="M1" t="str">
         <v>hook_size</v>
       </c>
+      <c r="N1" t="str">
+        <v>depth</v>
+      </c>
+      <c r="O1" t="str">
+        <v>action</v>
+      </c>
+      <c r="P1" t="str">
+        <v>subname</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>other.1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -48987,7 +48999,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M1058"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q1058"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -49210,7 +49222,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N143"/>
+  <dimension ref="A1:R143"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -49253,6 +49265,18 @@
         <v>hook_size</v>
       </c>
       <c r="N1" t="str">
+        <v>depth</v>
+      </c>
+      <c r="O1" t="str">
+        <v>action</v>
+      </c>
+      <c r="P1" t="str">
+        <v>subname</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>other.1</v>
+      </c>
+      <c r="R1" t="str">
         <v>quantity (入数)</v>
       </c>
     </row>
@@ -49296,7 +49320,7 @@
       <c r="M2" t="str">
         <v/>
       </c>
-      <c r="N2" t="str">
+      <c r="R2" t="str">
         <v/>
       </c>
     </row>
@@ -49340,7 +49364,7 @@
       <c r="M3" t="str">
         <v/>
       </c>
-      <c r="N3" t="str">
+      <c r="R3" t="str">
         <v/>
       </c>
     </row>
@@ -49384,7 +49408,7 @@
       <c r="M4" t="str">
         <v/>
       </c>
-      <c r="N4" t="str">
+      <c r="R4" t="str">
         <v/>
       </c>
     </row>
@@ -49428,7 +49452,7 @@
       <c r="M5" t="str">
         <v/>
       </c>
-      <c r="N5" t="str">
+      <c r="R5" t="str">
         <v/>
       </c>
     </row>
@@ -49472,7 +49496,7 @@
       <c r="M6" t="str">
         <v/>
       </c>
-      <c r="N6" t="str">
+      <c r="R6" t="str">
         <v/>
       </c>
     </row>
@@ -49516,7 +49540,7 @@
       <c r="M7" t="str">
         <v/>
       </c>
-      <c r="N7" t="str">
+      <c r="R7" t="str">
         <v/>
       </c>
     </row>
@@ -49560,7 +49584,7 @@
       <c r="M8" t="str">
         <v/>
       </c>
-      <c r="N8" t="str">
+      <c r="R8" t="str">
         <v/>
       </c>
     </row>
@@ -49604,7 +49628,7 @@
       <c r="M9" t="str">
         <v/>
       </c>
-      <c r="N9" t="str">
+      <c r="R9" t="str">
         <v/>
       </c>
     </row>
@@ -49648,7 +49672,7 @@
       <c r="M10" t="str">
         <v/>
       </c>
-      <c r="N10" t="str">
+      <c r="R10" t="str">
         <v/>
       </c>
     </row>
@@ -49692,7 +49716,7 @@
       <c r="M11" t="str">
         <v/>
       </c>
-      <c r="N11" t="str">
+      <c r="R11" t="str">
         <v/>
       </c>
     </row>
@@ -49736,7 +49760,7 @@
       <c r="M12" t="str">
         <v/>
       </c>
-      <c r="N12" t="str">
+      <c r="R12" t="str">
         <v/>
       </c>
     </row>
@@ -49780,7 +49804,7 @@
       <c r="M13" t="str">
         <v/>
       </c>
-      <c r="N13" t="str">
+      <c r="R13" t="str">
         <v/>
       </c>
     </row>
@@ -49824,7 +49848,7 @@
       <c r="M14" t="str">
         <v/>
       </c>
-      <c r="N14" t="str">
+      <c r="R14" t="str">
         <v/>
       </c>
     </row>
@@ -49868,7 +49892,7 @@
       <c r="M15" t="str">
         <v/>
       </c>
-      <c r="N15" t="str">
+      <c r="R15" t="str">
         <v/>
       </c>
     </row>
@@ -49912,7 +49936,7 @@
       <c r="M16" t="str">
         <v/>
       </c>
-      <c r="N16" t="str">
+      <c r="R16" t="str">
         <v/>
       </c>
     </row>
@@ -49956,7 +49980,7 @@
       <c r="M17" t="str">
         <v/>
       </c>
-      <c r="N17" t="str">
+      <c r="R17" t="str">
         <v/>
       </c>
     </row>
@@ -50000,7 +50024,7 @@
       <c r="M18" t="str">
         <v/>
       </c>
-      <c r="N18" t="str">
+      <c r="R18" t="str">
         <v/>
       </c>
     </row>
@@ -50044,7 +50068,7 @@
       <c r="M19" t="str">
         <v/>
       </c>
-      <c r="N19" t="str">
+      <c r="R19" t="str">
         <v/>
       </c>
     </row>
@@ -50088,7 +50112,7 @@
       <c r="M20" t="str">
         <v/>
       </c>
-      <c r="N20" t="str">
+      <c r="R20" t="str">
         <v/>
       </c>
     </row>
@@ -50132,7 +50156,7 @@
       <c r="M21" t="str">
         <v/>
       </c>
-      <c r="N21" t="str">
+      <c r="R21" t="str">
         <v/>
       </c>
     </row>
@@ -50176,7 +50200,7 @@
       <c r="M22" t="str">
         <v/>
       </c>
-      <c r="N22" t="str">
+      <c r="R22" t="str">
         <v/>
       </c>
     </row>
@@ -50220,7 +50244,7 @@
       <c r="M23" t="str">
         <v/>
       </c>
-      <c r="N23" t="str">
+      <c r="R23" t="str">
         <v/>
       </c>
     </row>
@@ -50264,7 +50288,7 @@
       <c r="M24" t="str">
         <v/>
       </c>
-      <c r="N24" t="str">
+      <c r="R24" t="str">
         <v/>
       </c>
     </row>
@@ -50308,7 +50332,7 @@
       <c r="M25" t="str">
         <v/>
       </c>
-      <c r="N25" t="str">
+      <c r="R25" t="str">
         <v/>
       </c>
     </row>
@@ -50352,7 +50376,7 @@
       <c r="M26" t="str">
         <v/>
       </c>
-      <c r="N26" t="str">
+      <c r="R26" t="str">
         <v/>
       </c>
     </row>
@@ -50396,7 +50420,7 @@
       <c r="M27" t="str">
         <v/>
       </c>
-      <c r="N27" t="str">
+      <c r="R27" t="str">
         <v/>
       </c>
     </row>
@@ -50440,7 +50464,7 @@
       <c r="M28" t="str">
         <v/>
       </c>
-      <c r="N28" t="str">
+      <c r="R28" t="str">
         <v/>
       </c>
     </row>
@@ -50484,7 +50508,7 @@
       <c r="M29" t="str">
         <v/>
       </c>
-      <c r="N29" t="str">
+      <c r="R29" t="str">
         <v/>
       </c>
     </row>
@@ -50528,7 +50552,7 @@
       <c r="M30" t="str">
         <v/>
       </c>
-      <c r="N30" t="str">
+      <c r="R30" t="str">
         <v/>
       </c>
     </row>
@@ -50572,7 +50596,7 @@
       <c r="M31" t="str">
         <v/>
       </c>
-      <c r="N31" t="str">
+      <c r="R31" t="str">
         <v/>
       </c>
     </row>
@@ -50616,7 +50640,7 @@
       <c r="M32" t="str">
         <v/>
       </c>
-      <c r="N32" t="str">
+      <c r="R32" t="str">
         <v/>
       </c>
     </row>
@@ -50660,7 +50684,7 @@
       <c r="M33" t="str">
         <v/>
       </c>
-      <c r="N33" t="str">
+      <c r="R33" t="str">
         <v/>
       </c>
     </row>
@@ -50704,7 +50728,7 @@
       <c r="M34" t="str">
         <v/>
       </c>
-      <c r="N34" t="str">
+      <c r="R34" t="str">
         <v/>
       </c>
     </row>
@@ -50748,7 +50772,7 @@
       <c r="M35" t="str">
         <v/>
       </c>
-      <c r="N35" t="str">
+      <c r="R35" t="str">
         <v/>
       </c>
     </row>
@@ -50792,7 +50816,7 @@
       <c r="M36" t="str">
         <v/>
       </c>
-      <c r="N36" t="str">
+      <c r="R36" t="str">
         <v/>
       </c>
     </row>
@@ -50836,7 +50860,7 @@
       <c r="M37" t="str">
         <v/>
       </c>
-      <c r="N37" t="str">
+      <c r="R37" t="str">
         <v/>
       </c>
     </row>
@@ -50880,7 +50904,7 @@
       <c r="M38" t="str">
         <v/>
       </c>
-      <c r="N38" t="str">
+      <c r="R38" t="str">
         <v/>
       </c>
     </row>
@@ -50924,7 +50948,7 @@
       <c r="M39" t="str">
         <v/>
       </c>
-      <c r="N39" t="str">
+      <c r="R39" t="str">
         <v/>
       </c>
     </row>
@@ -50968,7 +50992,7 @@
       <c r="M40" t="str">
         <v/>
       </c>
-      <c r="N40" t="str">
+      <c r="R40" t="str">
         <v/>
       </c>
     </row>
@@ -51012,7 +51036,7 @@
       <c r="M41" t="str">
         <v/>
       </c>
-      <c r="N41" t="str">
+      <c r="R41" t="str">
         <v/>
       </c>
     </row>
@@ -51056,7 +51080,7 @@
       <c r="M42" t="str">
         <v/>
       </c>
-      <c r="N42" t="str">
+      <c r="R42" t="str">
         <v/>
       </c>
     </row>
@@ -51100,7 +51124,7 @@
       <c r="M43" t="str">
         <v/>
       </c>
-      <c r="N43" t="str">
+      <c r="R43" t="str">
         <v/>
       </c>
     </row>
@@ -51144,7 +51168,7 @@
       <c r="M44" t="str">
         <v/>
       </c>
-      <c r="N44" t="str">
+      <c r="R44" t="str">
         <v/>
       </c>
     </row>
@@ -51188,7 +51212,7 @@
       <c r="M45" t="str">
         <v/>
       </c>
-      <c r="N45" t="str">
+      <c r="R45" t="str">
         <v/>
       </c>
     </row>
@@ -51232,7 +51256,7 @@
       <c r="M46" t="str">
         <v/>
       </c>
-      <c r="N46" t="str">
+      <c r="R46" t="str">
         <v/>
       </c>
     </row>
@@ -51276,7 +51300,7 @@
       <c r="M47" t="str">
         <v/>
       </c>
-      <c r="N47" t="str">
+      <c r="R47" t="str">
         <v/>
       </c>
     </row>
@@ -51320,7 +51344,7 @@
       <c r="M48" t="str">
         <v/>
       </c>
-      <c r="N48" t="str">
+      <c r="R48" t="str">
         <v/>
       </c>
     </row>
@@ -51364,7 +51388,7 @@
       <c r="M49" t="str">
         <v/>
       </c>
-      <c r="N49" t="str">
+      <c r="R49" t="str">
         <v/>
       </c>
     </row>
@@ -51408,7 +51432,7 @@
       <c r="M50" t="str">
         <v/>
       </c>
-      <c r="N50" t="str">
+      <c r="R50" t="str">
         <v>10</v>
       </c>
     </row>
@@ -51452,7 +51476,7 @@
       <c r="M51" t="str">
         <v/>
       </c>
-      <c r="N51" t="str">
+      <c r="R51" t="str">
         <v>8</v>
       </c>
     </row>
@@ -51496,7 +51520,7 @@
       <c r="M52" t="str">
         <v/>
       </c>
-      <c r="N52" t="str">
+      <c r="R52" t="str">
         <v>5</v>
       </c>
     </row>
@@ -51540,7 +51564,7 @@
       <c r="M53" t="str">
         <v/>
       </c>
-      <c r="N53" t="str">
+      <c r="R53" t="str">
         <v>5</v>
       </c>
     </row>
@@ -51584,7 +51608,7 @@
       <c r="M54" t="str">
         <v/>
       </c>
-      <c r="N54" t="str">
+      <c r="R54" t="str">
         <v>5</v>
       </c>
     </row>
@@ -51628,7 +51652,7 @@
       <c r="M55" t="str">
         <v/>
       </c>
-      <c r="N55" t="str">
+      <c r="R55" t="str">
         <v>5</v>
       </c>
     </row>
@@ -51672,7 +51696,7 @@
       <c r="M56" t="str">
         <v/>
       </c>
-      <c r="N56" t="str">
+      <c r="R56" t="str">
         <v>5</v>
       </c>
     </row>
@@ -51716,7 +51740,7 @@
       <c r="M57" t="str">
         <v/>
       </c>
-      <c r="N57" t="str">
+      <c r="R57" t="str">
         <v>5</v>
       </c>
     </row>
@@ -51760,7 +51784,7 @@
       <c r="M58" t="str">
         <v/>
       </c>
-      <c r="N58" t="str">
+      <c r="R58" t="str">
         <v>5</v>
       </c>
     </row>
@@ -51804,7 +51828,7 @@
       <c r="M59" t="str">
         <v/>
       </c>
-      <c r="N59" t="str">
+      <c r="R59" t="str">
         <v>5</v>
       </c>
     </row>
@@ -51848,7 +51872,7 @@
       <c r="M60" t="str">
         <v/>
       </c>
-      <c r="N60" t="str">
+      <c r="R60" t="str">
         <v>5</v>
       </c>
     </row>
@@ -51892,7 +51916,7 @@
       <c r="M61" t="str">
         <v/>
       </c>
-      <c r="N61" t="str">
+      <c r="R61" t="str">
         <v>5</v>
       </c>
     </row>
@@ -51936,7 +51960,7 @@
       <c r="M62" t="str">
         <v/>
       </c>
-      <c r="N62" t="str">
+      <c r="R62" t="str">
         <v>5</v>
       </c>
     </row>
@@ -51980,7 +52004,7 @@
       <c r="M63" t="str">
         <v/>
       </c>
-      <c r="N63" t="str">
+      <c r="R63" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52024,7 +52048,7 @@
       <c r="M64" t="str">
         <v/>
       </c>
-      <c r="N64" t="str">
+      <c r="R64" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52068,7 +52092,7 @@
       <c r="M65" t="str">
         <v/>
       </c>
-      <c r="N65" t="str">
+      <c r="R65" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52112,7 +52136,7 @@
       <c r="M66" t="str">
         <v/>
       </c>
-      <c r="N66" t="str">
+      <c r="R66" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52156,7 +52180,7 @@
       <c r="M67" t="str">
         <v/>
       </c>
-      <c r="N67" t="str">
+      <c r="R67" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52200,7 +52224,7 @@
       <c r="M68" t="str">
         <v/>
       </c>
-      <c r="N68" t="str">
+      <c r="R68" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52244,7 +52268,7 @@
       <c r="M69" t="str">
         <v/>
       </c>
-      <c r="N69" t="str">
+      <c r="R69" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52288,7 +52312,7 @@
       <c r="M70" t="str">
         <v/>
       </c>
-      <c r="N70" t="str">
+      <c r="R70" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52332,7 +52356,7 @@
       <c r="M71" t="str">
         <v/>
       </c>
-      <c r="N71" t="str">
+      <c r="R71" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52376,7 +52400,7 @@
       <c r="M72" t="str">
         <v/>
       </c>
-      <c r="N72" t="str">
+      <c r="R72" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52420,7 +52444,7 @@
       <c r="M73" t="str">
         <v/>
       </c>
-      <c r="N73" t="str">
+      <c r="R73" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52464,7 +52488,7 @@
       <c r="M74" t="str">
         <v/>
       </c>
-      <c r="N74" t="str">
+      <c r="R74" t="str">
         <v>2</v>
       </c>
     </row>
@@ -52508,7 +52532,7 @@
       <c r="M75" t="str">
         <v/>
       </c>
-      <c r="N75" t="str">
+      <c r="R75" t="str">
         <v>2</v>
       </c>
     </row>
@@ -52552,7 +52576,7 @@
       <c r="M76" t="str">
         <v/>
       </c>
-      <c r="N76" t="str">
+      <c r="R76" t="str">
         <v>2</v>
       </c>
     </row>
@@ -52596,7 +52620,7 @@
       <c r="M77" t="str">
         <v/>
       </c>
-      <c r="N77" t="str">
+      <c r="R77" t="str">
         <v>2</v>
       </c>
     </row>
@@ -52640,7 +52664,7 @@
       <c r="M78" t="str">
         <v/>
       </c>
-      <c r="N78" t="str">
+      <c r="R78" t="str">
         <v>2</v>
       </c>
     </row>
@@ -52684,7 +52708,7 @@
       <c r="M79" t="str">
         <v/>
       </c>
-      <c r="N79" t="str">
+      <c r="R79" t="str">
         <v>2</v>
       </c>
     </row>
@@ -52728,7 +52752,7 @@
       <c r="M80" t="str">
         <v/>
       </c>
-      <c r="N80" t="str">
+      <c r="R80" t="str">
         <v>12</v>
       </c>
     </row>
@@ -52772,7 +52796,7 @@
       <c r="M81" t="str">
         <v/>
       </c>
-      <c r="N81" t="str">
+      <c r="R81" t="str">
         <v>10</v>
       </c>
     </row>
@@ -52816,7 +52840,7 @@
       <c r="M82" t="str">
         <v/>
       </c>
-      <c r="N82" t="str">
+      <c r="R82" t="str">
         <v>10</v>
       </c>
     </row>
@@ -52860,7 +52884,7 @@
       <c r="M83" t="str">
         <v/>
       </c>
-      <c r="N83" t="str">
+      <c r="R83" t="str">
         <v>10</v>
       </c>
     </row>
@@ -52904,7 +52928,7 @@
       <c r="M84" t="str">
         <v/>
       </c>
-      <c r="N84" t="str">
+      <c r="R84" t="str">
         <v>10</v>
       </c>
     </row>
@@ -52948,7 +52972,7 @@
       <c r="M85" t="str">
         <v/>
       </c>
-      <c r="N85" t="str">
+      <c r="R85" t="str">
         <v>6</v>
       </c>
     </row>
@@ -52992,7 +53016,7 @@
       <c r="M86" t="str">
         <v/>
       </c>
-      <c r="N86" t="str">
+      <c r="R86" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53036,7 +53060,7 @@
       <c r="M87" t="str">
         <v/>
       </c>
-      <c r="N87" t="str">
+      <c r="R87" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53080,7 +53104,7 @@
       <c r="M88" t="str">
         <v/>
       </c>
-      <c r="N88" t="str">
+      <c r="R88" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53124,7 +53148,7 @@
       <c r="M89" t="str">
         <v/>
       </c>
-      <c r="N89" t="str">
+      <c r="R89" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53168,7 +53192,7 @@
       <c r="M90" t="str">
         <v/>
       </c>
-      <c r="N90" t="str">
+      <c r="R90" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53212,7 +53236,7 @@
       <c r="M91" t="str">
         <v/>
       </c>
-      <c r="N91" t="str">
+      <c r="R91" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53256,7 +53280,7 @@
       <c r="M92" t="str">
         <v/>
       </c>
-      <c r="N92" t="str">
+      <c r="R92" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53300,7 +53324,7 @@
       <c r="M93" t="str">
         <v/>
       </c>
-      <c r="N93" t="str">
+      <c r="R93" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53344,7 +53368,7 @@
       <c r="M94" t="str">
         <v/>
       </c>
-      <c r="N94" t="str">
+      <c r="R94" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53388,7 +53412,7 @@
       <c r="M95" t="str">
         <v/>
       </c>
-      <c r="N95" t="str">
+      <c r="R95" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53432,7 +53456,7 @@
       <c r="M96" t="str">
         <v/>
       </c>
-      <c r="N96" t="str">
+      <c r="R96" t="str">
         <v>7</v>
       </c>
     </row>
@@ -53476,7 +53500,7 @@
       <c r="M97" t="str">
         <v/>
       </c>
-      <c r="N97" t="str">
+      <c r="R97" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53520,7 +53544,7 @@
       <c r="M98" t="str">
         <v/>
       </c>
-      <c r="N98" t="str">
+      <c r="R98" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53564,7 +53588,7 @@
       <c r="M99" t="str">
         <v/>
       </c>
-      <c r="N99" t="str">
+      <c r="R99" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53608,7 +53632,7 @@
       <c r="M100" t="str">
         <v/>
       </c>
-      <c r="N100" t="str">
+      <c r="R100" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53652,7 +53676,7 @@
       <c r="M101" t="str">
         <v/>
       </c>
-      <c r="N101" t="str">
+      <c r="R101" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53696,7 +53720,7 @@
       <c r="M102" t="str">
         <v/>
       </c>
-      <c r="N102" t="str">
+      <c r="R102" t="str">
         <v>10</v>
       </c>
     </row>
@@ -53740,7 +53764,7 @@
       <c r="M103" t="str">
         <v/>
       </c>
-      <c r="N103" t="str">
+      <c r="R103" t="str">
         <v>8</v>
       </c>
     </row>
@@ -53784,7 +53808,7 @@
       <c r="M104" t="str">
         <v/>
       </c>
-      <c r="N104" t="str">
+      <c r="R104" t="str">
         <v>8</v>
       </c>
     </row>
@@ -53828,7 +53852,7 @@
       <c r="M105" t="str">
         <v/>
       </c>
-      <c r="N105" t="str">
+      <c r="R105" t="str">
         <v>8</v>
       </c>
     </row>
@@ -53872,7 +53896,7 @@
       <c r="M106" t="str">
         <v/>
       </c>
-      <c r="N106" t="str">
+      <c r="R106" t="str">
         <v>8</v>
       </c>
     </row>
@@ -53916,7 +53940,7 @@
       <c r="M107" t="str">
         <v/>
       </c>
-      <c r="N107" t="str">
+      <c r="R107" t="str">
         <v>8</v>
       </c>
     </row>
@@ -53960,7 +53984,7 @@
       <c r="M108" t="str">
         <v/>
       </c>
-      <c r="N108" t="str">
+      <c r="R108" t="str">
         <v>8</v>
       </c>
     </row>
@@ -54004,7 +54028,7 @@
       <c r="M109" t="str">
         <v/>
       </c>
-      <c r="N109" t="str">
+      <c r="R109" t="str">
         <v>7</v>
       </c>
     </row>
@@ -54048,7 +54072,7 @@
       <c r="M110" t="str">
         <v/>
       </c>
-      <c r="N110" t="str">
+      <c r="R110" t="str">
         <v>7</v>
       </c>
     </row>
@@ -54092,7 +54116,7 @@
       <c r="M111" t="str">
         <v/>
       </c>
-      <c r="N111" t="str">
+      <c r="R111" t="str">
         <v>7</v>
       </c>
     </row>
@@ -54136,7 +54160,7 @@
       <c r="M112" t="str">
         <v/>
       </c>
-      <c r="N112" t="str">
+      <c r="R112" t="str">
         <v>7</v>
       </c>
     </row>
@@ -54180,7 +54204,7 @@
       <c r="M113" t="str">
         <v/>
       </c>
-      <c r="N113" t="str">
+      <c r="R113" t="str">
         <v>7</v>
       </c>
     </row>
@@ -54224,7 +54248,7 @@
       <c r="M114" t="str">
         <v/>
       </c>
-      <c r="N114" t="str">
+      <c r="R114" t="str">
         <v>7</v>
       </c>
     </row>
@@ -54268,7 +54292,7 @@
       <c r="M115" t="str">
         <v/>
       </c>
-      <c r="N115" t="str">
+      <c r="R115" t="str">
         <v/>
       </c>
     </row>
@@ -54312,7 +54336,7 @@
       <c r="M116" t="str">
         <v/>
       </c>
-      <c r="N116" t="str">
+      <c r="R116" t="str">
         <v/>
       </c>
     </row>
@@ -54356,7 +54380,7 @@
       <c r="M117" t="str">
         <v/>
       </c>
-      <c r="N117" t="str">
+      <c r="R117" t="str">
         <v/>
       </c>
     </row>
@@ -54400,7 +54424,7 @@
       <c r="M118" t="str">
         <v/>
       </c>
-      <c r="N118" t="str">
+      <c r="R118" t="str">
         <v/>
       </c>
     </row>
@@ -54444,7 +54468,7 @@
       <c r="M119" t="str">
         <v/>
       </c>
-      <c r="N119" t="str">
+      <c r="R119" t="str">
         <v/>
       </c>
     </row>
@@ -54488,7 +54512,7 @@
       <c r="M120" t="str">
         <v/>
       </c>
-      <c r="N120" t="str">
+      <c r="R120" t="str">
         <v/>
       </c>
     </row>
@@ -54532,7 +54556,7 @@
       <c r="M121" t="str">
         <v/>
       </c>
-      <c r="N121" t="str">
+      <c r="R121" t="str">
         <v/>
       </c>
     </row>
@@ -54576,7 +54600,7 @@
       <c r="M122" t="str">
         <v/>
       </c>
-      <c r="N122" t="str">
+      <c r="R122" t="str">
         <v/>
       </c>
     </row>
@@ -54620,7 +54644,7 @@
       <c r="M123" t="str">
         <v/>
       </c>
-      <c r="N123" t="str">
+      <c r="R123" t="str">
         <v/>
       </c>
     </row>
@@ -54664,7 +54688,7 @@
       <c r="M124" t="str">
         <v/>
       </c>
-      <c r="N124" t="str">
+      <c r="R124" t="str">
         <v/>
       </c>
     </row>
@@ -54708,7 +54732,7 @@
       <c r="M125" t="str">
         <v/>
       </c>
-      <c r="N125" t="str">
+      <c r="R125" t="str">
         <v/>
       </c>
     </row>
@@ -54752,7 +54776,7 @@
       <c r="M126" t="str">
         <v/>
       </c>
-      <c r="N126" t="str">
+      <c r="R126" t="str">
         <v/>
       </c>
     </row>
@@ -54796,7 +54820,7 @@
       <c r="M127" t="str">
         <v/>
       </c>
-      <c r="N127" t="str">
+      <c r="R127" t="str">
         <v/>
       </c>
     </row>
@@ -54840,7 +54864,7 @@
       <c r="M128" t="str">
         <v/>
       </c>
-      <c r="N128" t="str">
+      <c r="R128" t="str">
         <v/>
       </c>
     </row>
@@ -54884,7 +54908,7 @@
       <c r="M129" t="str">
         <v/>
       </c>
-      <c r="N129" t="str">
+      <c r="R129" t="str">
         <v/>
       </c>
     </row>
@@ -54928,7 +54952,7 @@
       <c r="M130" t="str">
         <v/>
       </c>
-      <c r="N130" t="str">
+      <c r="R130" t="str">
         <v/>
       </c>
     </row>
@@ -54972,7 +54996,7 @@
       <c r="M131" t="str">
         <v/>
       </c>
-      <c r="N131" t="str">
+      <c r="R131" t="str">
         <v/>
       </c>
     </row>
@@ -55016,7 +55040,7 @@
       <c r="M132" t="str">
         <v/>
       </c>
-      <c r="N132" t="str">
+      <c r="R132" t="str">
         <v/>
       </c>
     </row>
@@ -55060,7 +55084,7 @@
       <c r="M133" t="str">
         <v/>
       </c>
-      <c r="N133" t="str">
+      <c r="R133" t="str">
         <v/>
       </c>
     </row>
@@ -55104,7 +55128,7 @@
       <c r="M134" t="str">
         <v/>
       </c>
-      <c r="N134" t="str">
+      <c r="R134" t="str">
         <v/>
       </c>
     </row>
@@ -55148,7 +55172,7 @@
       <c r="M135" t="str">
         <v/>
       </c>
-      <c r="N135" t="str">
+      <c r="R135" t="str">
         <v/>
       </c>
     </row>
@@ -55192,7 +55216,7 @@
       <c r="M136" t="str">
         <v/>
       </c>
-      <c r="N136" t="str">
+      <c r="R136" t="str">
         <v/>
       </c>
     </row>
@@ -55236,7 +55260,7 @@
       <c r="M137" t="str">
         <v/>
       </c>
-      <c r="N137" t="str">
+      <c r="R137" t="str">
         <v/>
       </c>
     </row>
@@ -55280,7 +55304,7 @@
       <c r="M138" t="str">
         <v/>
       </c>
-      <c r="N138" t="str">
+      <c r="R138" t="str">
         <v/>
       </c>
     </row>
@@ -55324,7 +55348,7 @@
       <c r="M139" t="str">
         <v/>
       </c>
-      <c r="N139" t="str">
+      <c r="R139" t="str">
         <v/>
       </c>
     </row>
@@ -55368,7 +55392,7 @@
       <c r="M140" t="str">
         <v/>
       </c>
-      <c r="N140" t="str">
+      <c r="R140" t="str">
         <v/>
       </c>
     </row>
@@ -55412,7 +55436,7 @@
       <c r="M141" t="str">
         <v/>
       </c>
-      <c r="N141" t="str">
+      <c r="R141" t="str">
         <v/>
       </c>
     </row>
@@ -55456,7 +55480,7 @@
       <c r="M142" t="str">
         <v/>
       </c>
-      <c r="N142" t="str">
+      <c r="R142" t="str">
         <v/>
       </c>
     </row>
@@ -55500,20 +55524,20 @@
       <c r="M143" t="str">
         <v/>
       </c>
-      <c r="N143" t="str">
+      <c r="R143" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N143"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R143"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:Q15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -55555,6 +55579,18 @@
       <c r="M1" t="str">
         <v>hook_size</v>
       </c>
+      <c r="N1" t="str">
+        <v>depth</v>
+      </c>
+      <c r="O1" t="str">
+        <v>action</v>
+      </c>
+      <c r="P1" t="str">
+        <v>subname</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>other.1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -56132,14 +56168,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M201"/>
+  <dimension ref="A1:Q201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -56181,6 +56217,18 @@
       <c r="M1" t="str">
         <v>hook_size</v>
       </c>
+      <c r="N1" t="str">
+        <v>depth</v>
+      </c>
+      <c r="O1" t="str">
+        <v>action</v>
+      </c>
+      <c r="P1" t="str">
+        <v>subname</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>other.1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -64384,7 +64432,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q201"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/pkgGear/data_raw/daiwa_lure_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/daiwa_lure_import.xlsx
@@ -480,7 +480,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K2" t="str">
-        <v>images/daiwa_lures/ハンクルミノー -スティーズカスタム-HMKL MINNOW - STEEZ CUSTOM -_HMKLMinnow-SteezCustom_AdelWakasagi.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%8F%E3%83%B3%E3%82%AF%E3%83%AB%E3%83%9F%E3%83%8E%E3%83%BC%20-%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0-HMKL%20MINNOW%20-%20STEEZ%20CUSTOM%20-_HMKLMinnow-SteezCustom_AdelWakasagi.jpg</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -524,7 +524,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K3" t="str">
-        <v>images/daiwa_lures/スティーズクランポSTEEZ CRANPO_STEEZ_CRANPO_81F_KAERU_4550133580918.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%AF%E3%83%A9%E3%83%B3%E3%83%9DSTEEZ%20CRANPO_STEEZ_CRANPO_81F_KAERU_4550133580918.jpg</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -568,7 +568,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K4" t="str">
-        <v>images/daiwa_lures/ふく魚／ちびふく魚FUKU UOCHIBI FUKU UO_FukuUo_CitrusChart.jpg</v>
+        <v/>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -612,7 +612,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K5" t="str">
-        <v>images/daiwa_lures/スティーズプロップSTEEZ PROP_SteezProp_70F_Kurokin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%97%E3%83%AD%E3%83%83%E3%83%97STEEZ%20PROP_SteezProp_70F_Kurokin.jpg</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -656,7 +656,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K6" t="str">
-        <v>images/daiwa_lures/スティーズ スプーンSTEEZ SPOON_SteezSpoon_Hasu.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B9%E3%83%97%E3%83%BC%E3%83%B3STEEZ%20SPOON_SteezSpoon_Hasu.png</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -700,7 +700,7 @@
         <v>glide</v>
       </c>
       <c r="K7" t="str">
-        <v>images/daiwa_lures/スティーズ アプナスジョイントSTEEZ APNAS JOINT_CHART_4550133464942.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%A2%E3%83%97%E3%83%8A%E3%82%B9%E3%82%B8%E3%83%A7%E3%82%A4%E3%83%B3%E3%83%88STEEZ%20APNAS%20JOINT_CHART_4550133464942.jpg</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -744,7 +744,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K8" t="str">
-        <v>images/daiwa_lures/スティーズクランクSTEEZ CRANK_22STEEZ_CRANK_700_MATTE_HOLO_WAKASAGI_4550133507472.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%AF%E3%83%A9%E3%83%B3%E3%82%AFSTEEZ%20CRANK_22STEEZ_CRANK_700_MATTE_HOLO_WAKASAGI_4550133507472.jpg</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -788,7 +788,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K9" t="str">
-        <v>images/daiwa_lures/バンクフラッターBANK FLUTTER_BankFlutter_ChartBack_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%90%E3%83%B3%E3%82%AF%E3%83%95%E3%83%A9%E3%83%83%E3%82%BF%E3%83%BCBANK%20FLUTTER_BankFlutter_ChartBack_1.jpg</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -832,7 +832,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K10" t="str">
-        <v>images/daiwa_lures/DジャークベイトD-JERKBAIT_D-JERKBAIT112F_SR-LI_LI_WAKASAGI_4550133665271.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/D%E3%82%B8%E3%83%A3%E3%83%BC%E3%82%AF%E3%83%99%E3%82%A4%E3%83%88D-JERKBAIT_D-JERKBAIT112F_SR-LI_LI_WAKASAGI_4550133665271.jpg</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -876,7 +876,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K11" t="str">
-        <v>images/daiwa_lures/スティーズ ツインバズSTEEZ TWIN BUZZ_STEEZ_TWIN_BUZZ_1-4OZ_MATTE_BLACK_4550133583315.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%84%E3%82%A4%E3%83%B3%E3%83%90%E3%82%BASTEEZ%20TWIN%20BUZZ_STEEZ_TWIN_BUZZ_1-4OZ_MATTE_BLACK_4550133583315.jpg</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -920,7 +920,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K12" t="str">
-        <v>images/daiwa_lures/スティーズ ダブルクラッチSTEEZ DOUBLE CLUTCH_SteezDoubleClutch_75SP_IPWakasagi.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81STEEZ%20DOUBLE%20CLUTCH_SteezDoubleClutch_75SP_IPWakasagi.jpg</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -964,7 +964,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K13" t="str">
-        <v>images/daiwa_lures/ちびふく零  ふく零  だいふく零CHIBI FUKU ZERO  FUKU ZERO  DAIFUKU ZERO_FukuZero_ChartBackBN.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%81%A1%E3%81%B3%E3%81%B5%E3%81%8F%E9%9B%B6%20%20%E3%81%B5%E3%81%8F%E9%9B%B6%20%20%E3%81%A0%E3%81%84%E3%81%B5%E3%81%8F%E9%9B%B6CHIBI%20FUKU%20ZERO%20%20FUKU%20ZERO%20%20DAIFUKU%20ZERO_FukuZero_ChartBackBN.jpg</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -1008,7 +1008,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K14" t="str">
-        <v>images/daiwa_lures/T.D.ハイパークランクT.D.HYPER CRANK_TD_HyperCrank_1064Ti_B-2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/T.D.%E3%83%8F%E3%82%A4%E3%83%91%E3%83%BC%E3%82%AF%E3%83%A9%E3%83%B3%E3%82%AFT.D.HYPER%20CRANK_TD_HyperCrank_1064Ti_B-2.jpg</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1052,7 +1052,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K15" t="str">
-        <v>images/daiwa_lures/スティーズバズベイトSTEEZ BUZZ BAIT_STEEZ_BUZZ_BAIT_1-2OZ_MATTE_BLACK_4550133578342.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%90%E3%82%BA%E3%83%99%E3%82%A4%E3%83%88STEEZ%20BUZZ%20BAIT_STEEZ_BUZZ_BAIT_1-2OZ_MATTE_BLACK_4550133578342.jpg</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1096,7 +1096,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K16" t="str">
-        <v>images/daiwa_lures/スティーズ ポッパーSTEEZ POPPER_STEEZ_POPPER_60F_RW_UMEKYO_ORANGE_4550133589317.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%9D%E3%83%83%E3%83%91%E3%83%BCSTEEZ%20POPPER_STEEZ_POPPER_60F_RW_UMEKYO_ORANGE_4550133589317.jpg</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1140,7 +1140,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K17" t="str">
-        <v>images/daiwa_lures/タイニースティーズクランクTINY STEEZ CRANK_TINY_STEEZ_CRANK_200_CITRUS_SHAD_4550133509193.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%BF%E3%82%A4%E3%83%8B%E3%83%BC%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%AF%E3%83%A9%E3%83%B3%E3%82%AFTINY%20STEEZ%20CRANK_TINY_STEEZ_CRANK_200_CITRUS_SHAD_4550133509193.jpg</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1184,7 +1184,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K18" t="str">
-        <v>images/daiwa_lures/ドラウンシケーダ REV JrDROWN CICADA REV Jr_DROWN_CICADA_REV_CLEAR_BROWN_4550133081736.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%89%E3%83%A9%E3%82%A6%E3%83%B3%E3%82%B7%E3%82%B1%E3%83%BC%E3%83%80%20REV%20JrDROWN%20CICADA%20REV%20Jr_DROWN_CICADA_REV_CLEAR_BROWN_4550133081736.jpg</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1228,7 +1228,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K19" t="str">
-        <v>images/daiwa_lures/T.D.ミノーT.D. MINNOW_TDMinnow_95SP_GhostAyu.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/T.D.%E3%83%9F%E3%83%8E%E3%83%BCT.D.%20MINNOW_TDMinnow_95SP_GhostAyu.jpg</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1272,7 +1272,7 @@
         <v>variable</v>
       </c>
       <c r="K20" t="str">
-        <v>images/daiwa_lures/スティーズ シャッドSTEEZ SHAD_SteezShad_54SPMR_Wakasagi.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B7%E3%83%A3%E3%83%83%E3%83%89STEEZ%20SHAD_SteezShad_54SPMR_Wakasagi.jpg</v>
       </c>
       <c r="L20" t="str">
         <v/>
@@ -1316,7 +1316,7 @@
         <v>variable</v>
       </c>
       <c r="K21" t="str">
-        <v>images/daiwa_lures/スティーズ サイレントシャッドSTEEZ SILENT SHAD_STEEZ_SILENT_SHAD_54SP_SR_AKABANE_SHAD_4550133404993.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B5%E3%82%A4%E3%83%AC%E3%83%B3%E3%83%88%E3%82%B7%E3%83%A3%E3%83%83%E3%83%89STEEZ%C2%A0SILENT%C2%A0SHAD_STEEZ_SILENT_SHAD_54SP_SR_AKABANE_SHAD_4550133404993.jpg</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1360,7 +1360,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K22" t="str">
-        <v>images/daiwa_lures/スティーズスクエアSTEEZ SQUARE_25STEEZ_SQUARE_100_BLUE_BACK_CHART_4550133580994.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%B9%E3%82%AF%E3%82%A8%E3%82%A2STEEZ%20SQUARE_25STEEZ_SQUARE_100_BLUE_BACK_CHART_4550133580994.jpg</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1404,7 +1404,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K23" t="str">
-        <v>images/daiwa_lures/ドラウンドラゴンフライDROWN DRAGONFLY_DROWNDRAGONFLY_ONIYANMA_4550133472619.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%89%E3%83%A9%E3%82%A6%E3%83%B3%E3%83%89%E3%83%A9%E3%82%B4%E3%83%B3%E3%83%95%E3%83%A9%E3%82%A4DROWN%20DRAGONFLY_DROWNDRAGONFLY_ONIYANMA_4550133472619.jpg</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1448,7 +1448,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K24" t="str">
-        <v>images/daiwa_lures/ふく鯰だいふく鯰FUKU NAMAZUDAIFUKU NAMAZU_FukuNamazu_Namazu.jpg</v>
+        <v/>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1492,7 +1492,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K25" t="str">
-        <v>images/daiwa_lures/ギルネードGILLNADO_Gillnado50S_SightKurokin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AE%E3%83%AB%E3%83%8D%E3%83%BC%E3%83%89GILLNADO_Gillnado50S_SightKurokin.jpg</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1536,7 +1536,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K26" t="str">
-        <v>images/daiwa_lures/ガストネードGUSTNADO_GUSTNADO55S_SIGHT_SHINER_4550133307324.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AC%E3%82%B9%E3%83%88%E3%83%8D%E3%83%BC%E3%83%89GUSTNADO_GUSTNADO55S_SIGHT_SHINER_4550133307324.jpg</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1580,7 +1580,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K27" t="str">
-        <v>images/daiwa_lures/スティーズ アスロックSTEEZ ASROC_SteezAsroc_SliverWhite.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%A2%E3%82%B9%E3%83%AD%E3%83%83%E3%82%AFSTEEZ%20ASROC_SteezAsroc_SliverWhite.jpg</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1624,7 +1624,7 @@
         <v>spin_flash</v>
       </c>
       <c r="K28" t="str">
-        <v>images/daiwa_lures/スティーズ スピナーベイトSTEEZ SPINNER BAIT_STEEZ_SPINNER_BAIT_38OZ_TW_SILVER_WHITE.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B9%E3%83%94%E3%83%8A%E3%83%BC%E3%83%99%E3%82%A4%E3%83%88STEEZ%20SPINNER%20BAIT_STEEZ_SPINNER_BAIT_38OZ_TW_SILVER_WHITE.jpg</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1668,7 +1668,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K29" t="str">
-        <v>images/daiwa_lures/ふく平FUKU HIRA_FUKU_HIRA_CITRUS_CHART_4550133559686.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%81%B5%E3%81%8F%E5%B9%B3FUKU%20HIRA_FUKU_HIRA_CITRUS_CHART_4550133559686.jpg</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1712,7 +1712,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K30" t="str">
-        <v>images/daiwa_lures/ふく弐FUKU 2_FUKU_2_CITRUS_CHART_4550133581090.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%81%B5%E3%81%8F%E5%BC%90FUKU%202_FUKU_2_CITRUS_CHART_4550133581090.jpg</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -1756,7 +1756,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K31" t="str">
-        <v>images/daiwa_lures/スティーズイグラSTEEZ IGLA_STEEZ_IGLA_14OZ_TYPE_INDIANA_SILVER_WHITE_4550133566738.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%A4%E3%82%B0%E3%83%A9STEEZ%20IGLA_STEEZ_IGLA_14OZ_TYPE_INDIANA_SILVER_WHITE_4550133566738.jpg</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -1800,7 +1800,7 @@
         <v>walk_pop</v>
       </c>
       <c r="K32" t="str">
-        <v>images/daiwa_lures/スティーズ ペンシルSTEEZ PENCIL_SteezPencil_60F_Wakasagi.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%9A%E3%83%B3%E3%82%B7%E3%83%ABSTEEZ%20PENCIL_SteezPencil_60F_Wakasagi.jpg</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1844,7 +1844,7 @@
         <v>variable</v>
       </c>
       <c r="K33" t="str">
-        <v>images/daiwa_lures/ちびふくシャッド弐  ふくシャッド弐CHIBI FUKU SHAD 2  FUKU SHAD 2_FUKU_SHAD_2_CITRUS_CHART_4550133504716.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%81%A1%E3%81%B3%E3%81%B5%E3%81%8F%E3%82%B7%E3%83%A3%E3%83%83%E3%83%89%E5%BC%90%20%20%E3%81%B5%E3%81%8F%E3%82%B7%E3%83%A3%E3%83%83%E3%83%89%E5%BC%90CHIBI%20FUKU%20SHAD%202%20%20FUKU%20SHAD%202_FUKU_SHAD_2_CITRUS_CHART_4550133504716.jpg</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1888,7 +1888,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K34" t="str">
-        <v>images/daiwa_lures/スティーズ カバーチャターSTEEZ COVER CHATTER_25STEEZ_COVER_CHATTER_3-8_BLACK_4550133578205.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%AB%E3%83%90%E3%83%BC%E3%83%81%E3%83%A3%E3%82%BF%E3%83%BCSTEEZ%20COVER%20CHATTER_25STEEZ_COVER_CHATTER_3-8_BLACK_4550133578205.jpg</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -1932,7 +1932,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K35" t="str">
-        <v>images/daiwa_lures/ふく壱  ちびふく壱FUKU ICHI  CHIBI FUKU ICHI_FukuIchi_Torafugu.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%81%B5%E3%81%8F%E5%A3%B1%20%20%E3%81%A1%E3%81%B3%E3%81%B5%E3%81%8F%E5%A3%B1FUKU%20ICHI%20%20CHIBI%20FUKU%20ICHI_FukuIchi_Torafugu.jpg</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -1976,7 +1976,7 @@
         <v>vibration</v>
       </c>
       <c r="K36" t="str">
-        <v>images/daiwa_lures/スティーズメタルバイブスリムSTEEZ METAL VIB SLIM_STEEZ_METAL_VIB_SLIM_8G_ADEL_WAKASAGI_4550133447464.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%A1%E3%82%BF%E3%83%AB%E3%83%90%E3%82%A4%E3%83%96%E3%82%B9%E3%83%AA%E3%83%A0STEEZ%20METAL%20VIB%20SLIM_STEEZ_METAL_VIB_SLIM_8G_ADEL_WAKASAGI_4550133447464.jpg</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -2020,7 +2020,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K37" t="str">
-        <v>images/daiwa_lures/キッケルウォーカーキッケルウォーカー BIGKIKKER WALKERKIKKER WALKER BIG_KIKKER_WALKER_SUJIEBI_GREEN_FLAKE_4550133559778.jpg</v>
+        <v/>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -2064,7 +2064,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K38" t="str">
-        <v>images/daiwa_lures/カシューナッツCASHEW NUT_CASHEW_NUTS_KUROKIN_4550133567131.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AB%E3%82%B7%E3%83%A5%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84CASHEW%20NUT_CASHEW_NUTS_KUROKIN_4550133567131.jpg</v>
       </c>
       <c r="L38" t="str">
         <v/>
@@ -2108,7 +2108,7 @@
         <v>vibration</v>
       </c>
       <c r="K39" t="str">
-        <v>images/daiwa_lures/T.D.バイブレーションT.D.VIBRATION_TD_Vibration_74S_Wakasagi.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/T.D.%E3%83%90%E3%82%A4%E3%83%96%E3%83%AC%E3%83%BC%E3%82%B7%E3%83%A7%E3%83%B3T.D.VIBRATION_TD_Vibration_74S_Wakasagi.jpg</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -2152,7 +2152,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K40" t="str">
-        <v>images/daiwa_lures/ラトリンチューブキックスRATTLIN' TUBE KICKS_4_SnowWhiteShrimp.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%A9%E3%83%88%E3%83%AA%E3%83%B3%E3%83%81%E3%83%A5%E3%83%BC%E3%83%96%E3%82%AD%E3%83%83%E3%82%AF%E3%82%B9RATTLIN'%20TUBE%20KICKS_4_SnowWhiteShrimp.jpg</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -2196,7 +2196,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K41" t="str">
-        <v>images/daiwa_lures/ワイルドピーナッツ  タイニーワイルドピーナッツWILD PEANUT  TINY WILD PEANUT_WildPeanut_KinkirakinCraw.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%AF%E3%82%A4%E3%83%AB%E3%83%89%E3%83%94%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84%20%20%E3%82%BF%E3%82%A4%E3%83%8B%E3%83%BC%E3%83%AF%E3%82%A4%E3%83%AB%E3%83%89%E3%83%94%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84WILD%20PEANUT%20%20TINY%20WILD%20PEANUT_WildPeanut_KinkirakinCraw.jpg</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -2240,7 +2240,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K42" t="str">
-        <v>images/daiwa_lures/アーモンドALMOND_ALMOND_KUROKIN_4550133566639.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%A2%E3%83%BC%E3%83%A2%E3%83%B3%E3%83%89ALMOND_ALMOND_KUROKIN_4550133566639.jpg</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -2284,7 +2284,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K43" t="str">
-        <v>images/daiwa_lures/スティーズ ブラーモSTEEZ BRAMO_7_GREEN-PUMPKIN_4550133457630.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%96%E3%83%A9%E3%83%BC%E3%83%A2STEEZ%20BRAMO_7_GREEN-PUMPKIN_4550133457630.jpg</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2328,7 +2328,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K44" t="str">
-        <v>images/daiwa_lures/デカピーナッツ IIDEKA PEANUT II_DekaPeanutII_SSR_BlackChartBerry.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%87%E3%82%AB%E3%83%94%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84%20IIDEKA%20PEANUT%20II_DekaPeanutII_SSR_BlackChartBerry.jpg</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2372,7 +2372,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K45" t="str">
-        <v>images/daiwa_lures/ピーナッツPEANUT_Peanut_SR_SexyShad.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%94%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84PEANUT_Peanut_SR_SexyShad.jpg</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2416,7 +2416,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K46" t="str">
-        <v>images/daiwa_lures/スティーズバンクハッカークローSTEEZ BANK HACKER CRAW_STEEZ_BANK_HACKER_CLAW_GREEN_PUMPKIN_4550133566899.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%90%E3%83%B3%E3%82%AF%E3%83%8F%E3%83%83%E3%82%AB%E3%83%BC%E3%82%AF%E3%83%AD%E3%83%BCSTEEZ%20BANK%20HACKER%20CRAW_STEEZ_BANK_HACKER_CLAW_GREEN_PUMPKIN_4550133566899.jpg</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2460,7 +2460,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K47" t="str">
-        <v>images/daiwa_lures/ムーブベイトMOVE BAIT_MoveBait_31_GreenPumpkin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%A0%E3%83%BC%E3%83%96%E3%83%99%E3%82%A4%E3%83%88MOVE%20BAIT_MoveBait_31_GreenPumpkin.jpg</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2504,7 +2504,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K48" t="str">
-        <v>images/daiwa_lures/タイニーピーナッツTINY PEANUT_TinyPeanuts_SR_KuroKin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%BF%E3%82%A4%E3%83%8B%E3%83%BC%E3%83%94%E3%83%BC%E3%83%8A%E3%83%83%E3%83%84TINY%20PEANUT_TinyPeanuts_SR_KuroKin.jpg</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2548,7 +2548,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K49" t="str">
-        <v>images/daiwa_lures/スティーズクローSTEEZ CRAW_1_GREEN_PUMPKIN_4550133464546.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%82%AF%E3%83%AD%E3%83%BCSTEEZ%20CRAW_1_GREEN_PUMPKIN_4550133464546.jpg</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2592,7 +2592,7 @@
         <v>variable</v>
       </c>
       <c r="K50" t="str">
-        <v>images/daiwa_lures/ムーブホグMOVE HOG_3_GREEN_PUMPKIN_4550133566974.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%A0%E3%83%BC%E3%83%96%E3%83%9B%E3%82%B0MOVE%20HOG_3_GREEN_PUMPKIN_4550133566974.jpg</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2636,7 +2636,7 @@
         <v>glide</v>
       </c>
       <c r="K51" t="str">
-        <v>images/daiwa_lures/スティーズ アプナスバグSTEEZ APNAS BUG_STEEZ-APNAS-BUG-GREEN-PUMPKIN-BLUE-FLAKE_4550133465024.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%A2%E3%83%97%E3%83%8A%E3%82%B9%E3%83%90%E3%82%B0STEEZ%20APNAS%20BUG_STEEZ-APNAS-BUG-GREEN-PUMPKIN-BLUE-FLAKE_4550133465024.jpg</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2680,7 +2680,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K52" t="str">
-        <v>images/daiwa_lures/スティーズ ポップクラッカーSTEEZ POP CRACKER_1_NUDE_BROWN_4550133354410.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%9D%E3%83%83%E3%83%97%E3%82%AF%E3%83%A9%E3%83%83%E3%82%AB%E3%83%BCSTEEZ%20POP%20CRACKER_1_NUDE_BROWN_4550133354410.jpg</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2724,7 +2724,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K53" t="str">
-        <v>images/daiwa_lures/スティーズ スターリングフィッシュSTEEZ STIRRING FISH_3_BIWAKO_AYU_4550133399077.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B9%E3%82%BF%E3%83%BC%E3%83%AA%E3%83%B3%E3%82%B0%E3%83%95%E3%82%A3%E3%83%83%E3%82%B7%E3%83%A5STEEZ%20STIRRING%20FISH_3_BIWAKO_AYU_4550133399077.jpg</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2768,7 +2768,7 @@
         <v>variable</v>
       </c>
       <c r="K54" t="str">
-        <v>images/daiwa_lures/シュリンピード／シュリンピードJr.SHRIMPEDE／SHRIMPEDE Jr._Shrimpede_GreenPumpkin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%A5%E3%83%AA%E3%83%B3%E3%83%94%E3%83%BC%E3%83%89%EF%BC%8F%E3%82%B7%E3%83%A5%E3%83%AA%E3%83%B3%E3%83%94%E3%83%BC%E3%83%89Jr.SHRIMPEDE%EF%BC%8FSHRIMPEDE%20Jr._Shrimpede_GreenPumpkin.jpg</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2812,7 +2812,7 @@
         <v>variable</v>
       </c>
       <c r="K55" t="str">
-        <v>images/daiwa_lures/キッケルカーリーKIKKER CURLY_melon_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AD%E3%83%83%E3%82%B1%E3%83%AB%E3%82%AB%E3%83%BC%E3%83%AA%E3%83%BCKIKKER%20CURLY_melon_1.jpg</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -2856,7 +2856,7 @@
         <v>variable</v>
       </c>
       <c r="K56" t="str">
-        <v>images/daiwa_lures/スティーズネコストレートSTEEZ NEKO STRAIGHT_75_GREEN_PUMPKIN_BLUE_FLAKE_4550133564222.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%8D%E3%82%B3%E3%82%B9%E3%83%88%E3%83%AC%E3%83%BC%E3%83%88STEEZ%20NEKO%20STRAIGHT_75_GREEN_PUMPKIN_BLUE_FLAKE_4550133564222.jpg</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -2900,7 +2900,7 @@
         <v>variable</v>
       </c>
       <c r="K57" t="str">
-        <v>images/daiwa_lures/スティーズ ホグSTEEZ HOG_SteezHog_GreenPumpkin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%9B%E3%82%B0STEEZ%20HOG_SteezHog_GreenPumpkin.jpg</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -2944,7 +2944,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K58" t="str">
-        <v>images/daiwa_lures/スティーズ パワーフィネスジグSTEEZ POWERFINESSEJIG_5G_GREEN_PUMPKIM_BLUE_FLAKE_4550133464140.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%91%E3%83%AF%E3%83%BC%E3%83%95%E3%82%A3%E3%83%8D%E3%82%B9%E3%82%B8%E3%82%B0STEEZ%20POWERFINESSEJIG_5G_GREEN_PUMPKIM_BLUE_FLAKE_4550133464140.jpg</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -2988,7 +2988,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K59" t="str">
-        <v>images/daiwa_lures/スティーズ リアルスラッガーSTEEZ REAL SLUGGER_7-SILVER-WAKASAGI_4550133448171.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%AA%E3%82%A2%E3%83%AB%E3%82%B9%E3%83%A9%E3%83%83%E3%82%AC%E3%83%BCSTEEZ%20REAL%20SLUGGER_7-SILVER-WAKASAGI_4550133448171.jpg</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -3032,7 +3032,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K60" t="str">
-        <v>images/daiwa_lures/スティーズ　ネコファットSTEEZ NEKO FAT_2_GREEN_PUMPKIN_4550133614842.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%80%80%E3%83%8D%E3%82%B3%E3%83%95%E3%82%A1%E3%83%83%E3%83%88STEEZ%20NEKO%20FAT_2_GREEN_PUMPKIN_4550133614842.jpg</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -3076,7 +3076,7 @@
         <v>variable</v>
       </c>
       <c r="K61" t="str">
-        <v>images/daiwa_lures/スティーズ フィネスストレートSTEEZ FINESSE STRAIGHT_3_YAMA-P_EBIMISO_4550133559853.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%95%E3%82%A3%E3%83%8D%E3%82%B9%E3%82%B9%E3%83%88%E3%83%AC%E3%83%BC%E3%83%88STEEZ%20FINESSE%20STRAIGHT_3_YAMA-P_EBIMISO_4550133559853.jpg</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -3120,7 +3120,7 @@
         <v>variable</v>
       </c>
       <c r="K62" t="str">
-        <v>images/daiwa_lures/スティーズネコストレートロングSTEEZ NEKO STRAIGHT LONG_STEEZ_NEKO_STRAIGHT_LONG_9_MIMIZU_4550133536052.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%8D%E3%82%B3%E3%82%B9%E3%83%88%E3%83%AC%E3%83%BC%E3%83%88%E3%83%AD%E3%83%B3%E3%82%B0STEEZ%20NEKO%20STRAIGHT%20LONG_STEEZ_NEKO_STRAIGHT_LONG_9_MIMIZU_4550133536052.jpg</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -3164,7 +3164,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K63" t="str">
-        <v>images/daiwa_lures/スティーズ スターリングツインSTEEZ STIRRING TWIN_STEEZStirringTwin_GreenPumpkin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B9%E3%82%BF%E3%83%BC%E3%83%AA%E3%83%B3%E3%82%B0%E3%83%84%E3%82%A4%E3%83%B3STEEZ%20STIRRING%20TWIN_STEEZStirringTwin_GreenPumpkin.jpg</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3208,7 +3208,7 @@
         <v>variable</v>
       </c>
       <c r="K64" t="str">
-        <v>images/daiwa_lures/スティーズ スターリングシャッドSTEEZ STIRRING SHAD_SteezStirringShad_28_MagicShad.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%82%B9%E3%82%BF%E3%83%BC%E3%83%AA%E3%83%B3%E3%82%B0%E3%82%B7%E3%83%A3%E3%83%83%E3%83%89STEEZ%20STIRRING%20SHAD_SteezStirringShad_28_MagicShad.jpg</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3252,7 +3252,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K65" t="str">
-        <v>images/daiwa_lures/BHカバージグBH COVER JIG_BH_COVER_JIG_10G_BLACK_4550133506192.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/BH%E3%82%AB%E3%83%90%E3%83%BC%E3%82%B8%E3%82%B0BH%20COVER%20JIG_BH_COVER_JIG_10G_BLACK_4550133506192.jpg</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3296,7 +3296,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K66" t="str">
-        <v>images/daiwa_lures/BHマルチジグBH MULTI JIG_BH_MULTI_JIG_10G_BLACK_4550133505089.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/BH%E3%83%9E%E3%83%AB%E3%83%81%E3%82%B8%E3%82%B0BH%20MULTI%20JIG_BH_MULTI_JIG_10G_BLACK_4550133505089.jpg</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -3340,7 +3340,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K67" t="str">
-        <v>images/daiwa_lures/スティーズ パワーフィネスジグ TYPEカバーSTEEZ POWERFINESSEJIG TYPECOVER_7G-GREEN-PUMPKIM-BULE-FLAKE_4550133464461.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%91%E3%83%AF%E3%83%BC%E3%83%95%E3%82%A3%E3%83%8D%E3%82%B9%E3%82%B8%E3%82%B0%20TYPE%E3%82%AB%E3%83%90%E3%83%BCSTEEZ%20POWERFINESSEJIG%20TYPECOVER_7G-GREEN-PUMPKIM-BULE-FLAKE_4550133464461.jpg</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -3384,7 +3384,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K68" t="str">
-        <v>images/daiwa_lures/BHジグスピナーBH JIG SPINNER_BH_JIG_SPINNER_7_WAKASAGI_4550133508424.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/BH%E3%82%B8%E3%82%B0%E3%82%B9%E3%83%94%E3%83%8A%E3%83%BCBH%20JIG%20SPINNER_BH_JIG_SPINNER_7_WAKASAGI_4550133508424.jpg</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -3428,7 +3428,7 @@
         <v>flutter_fall</v>
       </c>
       <c r="K69" t="str">
-        <v>images/daiwa_lures/BHミニジグBH MINI JIG_2G_GREEN_PUMPKIN_4550133505812.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/BH%E3%83%9F%E3%83%8B%E3%82%B8%E3%82%B0BH%20MINI%20JIG_2G_GREEN_PUMPKIN_4550133505812.jpg</v>
       </c>
       <c r="L69" t="str">
         <v/>
@@ -3472,7 +3472,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K70" t="str">
-        <v>images/daiwa_lures/シルバークリークミノージョイントSILVER CREEK MINNOW JOINT_SILVER_CREEK_MINNOW_JOINT_50S_CHART_YAMAME_OB_4550133460609.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BC%E3%82%B8%E3%83%A7%E3%82%A4%E3%83%B3%E3%83%88SILVER%20CREEK%20MINNOW%20JOINT_SILVER_CREEK_MINNOW_JOINT_50S_CHART_YAMAME_OB_4550133460609.jpg</v>
       </c>
       <c r="L70" t="str">
         <v/>
@@ -3516,7 +3516,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K71" t="str">
-        <v>images/daiwa_lures/シルバークリークミノーSILVER CREEK MINNOW_SilverCreekMinnow_40S_Akakin.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BCSILVER%20CREEK%20MINNOW_SilverCreekMinnow_40S_Akakin.jpg</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -3560,7 +3560,7 @@
         <v>vibration</v>
       </c>
       <c r="K72" t="str">
-        <v>images/daiwa_lures/BHメタルバイブBH METAL VIB_BH_METAL_VIB_5G_WAKASAGI_4550133508790.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/BH%E3%83%A1%E3%82%BF%E3%83%AB%E3%83%90%E3%82%A4%E3%83%96BH%20METAL%20VIB_BH_METAL_VIB_5G_WAKASAGI_4550133508790.jpg</v>
       </c>
       <c r="L72" t="str">
         <v/>
@@ -3604,7 +3604,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K73" t="str">
-        <v>images/daiwa_lures/ダブルクラッチF1 C&amp;R カスタムDOUBLECLUTCH F1 C&amp;R CUSTOM_DOUBLECLUTCH45F1CRCUSTOMCHARTYAMAMEORANGEBELLY4550133564703.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81F1%20C%26R%20%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0DOUBLECLUTCH%20F1%20C%26R%20CUSTOM_DOUBLECLUTCH45F1CRCUSTOMCHARTYAMAMEORANGEBELLY4550133564703.jpg</v>
       </c>
       <c r="L73" t="str">
         <v/>
@@ -3648,7 +3648,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K74" t="str">
-        <v>images/daiwa_lures/シルバークリークミノーTGSILVER CREEK MINNOW TG_SILVER_CREEK_MINNOW_TG_50S-LI_LI_CHART_YAMAME_4550133687860.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BCTGSILVER%20CREEK%20MINNOW%20TG_SILVER_CREEK_MINNOW_TG_50S-LI_LI_CHART_YAMAME_4550133687860.jpg</v>
       </c>
       <c r="L74" t="str">
         <v/>
@@ -3692,7 +3692,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K75" t="str">
-        <v>images/daiwa_lures/シルバークリークミノーダートカスタムSILVER CREEK MINNOW DART CUSTOM_SilverCreekMinnowDartCustom_48S_Yamame.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BC%E3%83%80%E3%83%BC%E3%83%88%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0SILVER%20CREEK%20MINNOW%20DART%20CUSTOM_SilverCreekMinnowDartCustom_48S_Yamame.jpg</v>
       </c>
       <c r="L75" t="str">
         <v/>
@@ -3736,7 +3736,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K76" t="str">
-        <v>images/daiwa_lures/ワブクラ30DR  C&amp;R カスタムWABCRA30DR C&amp;R CUSTOM_WABCRA30DRCRCUSTOMCHARTYAMAMEORANGEBELLY4550133564765.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%AF%E3%83%96%E3%82%AF%E3%83%A930DR%20%20C%26R%20%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0WABCRA30DR%20C%26R%20CUSTOM_WABCRA30DRCRCUSTOMCHARTYAMAMEORANGEBELLY4550133564765.jpg</v>
       </c>
       <c r="L76" t="str">
         <v/>
@@ -3780,7 +3780,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K77" t="str">
-        <v>images/daiwa_lures/ドクターミノーIIジョイントDr.MINNOW II JOINT_DrMinnow2J_50S_Yamame.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9F%E3%83%8E%E3%83%BCII%E3%82%B8%E3%83%A7%E3%82%A4%E3%83%B3%E3%83%88Dr.MINNOW%20II%20JOINT_DrMinnow2J_50S_Yamame.jpg</v>
       </c>
       <c r="L77" t="str">
         <v/>
@@ -3824,7 +3824,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K78" t="str">
-        <v>images/daiwa_lures/シルバークリークミノーダイビングカスタムSILVER CREEK MINNOW DIVING CUSTOM_SilverCreekMinnowDivingCustom50FS_ChartYamameOB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BC%E3%83%80%E3%82%A4%E3%83%93%E3%83%B3%E3%82%B0%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0SILVER%20CREEK%20MINNOW%20DIVING%20CUSTOM_SilverCreekMinnowDivingCustom50FS_ChartYamameOB.jpg</v>
       </c>
       <c r="L78" t="str">
         <v/>
@@ -3868,7 +3868,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K79" t="str">
-        <v>images/daiwa_lures/シルバークリークミノースローフォールカスタムSILVER CREEK MINNOW SLOW FALL CUSTOM_SilverCreekMinnowFallCustom_40SS_ChartYamameOrangeBerry.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%E3%83%9F%E3%83%8E%E3%83%BC%E3%82%B9%E3%83%AD%E3%83%BC%E3%83%95%E3%82%A9%E3%83%BC%E3%83%AB%E3%82%AB%E3%82%B9%E3%82%BF%E3%83%A0SILVER%20CREEK%20MINNOW%20SLOW%20FALL%20CUSTOM_SilverCreekMinnowFallCustom_40SS_ChartYamameOrangeBerry.jpg</v>
       </c>
       <c r="L79" t="str">
         <v/>
@@ -3912,7 +3912,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K80" t="str">
-        <v>images/daiwa_lures/DR.ミノー2DR. MINNOW Ⅱ_MINNOW2_Yamame.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/DR.%E3%83%9F%E3%83%8E%E3%83%BC2DR.%20MINNOW%20%E2%85%A1_MINNOW2_Yamame.jpg</v>
       </c>
       <c r="L80" t="str">
         <v/>
@@ -3956,7 +3956,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K81" t="str">
-        <v>images/daiwa_lures/チヌーク SCHINOOK S_ChinookS_DoPink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%81%E3%83%8C%E3%83%BC%E3%82%AF%20SCHINOOK%20S_ChinookS_DoPink.jpg</v>
       </c>
       <c r="L81" t="str">
         <v/>
@@ -4000,7 +4000,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K82" t="str">
-        <v>images/daiwa_lures/クルセイダー激アツCRUSADER GEKIATSU_CrusaderGekiAtsu_YamameOB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AF%E3%83%AB%E3%82%BB%E3%82%A4%E3%83%80%E3%83%BC%E6%BF%80%E3%82%A2%E3%83%84CRUSADER%20GEKIATSU_CrusaderGekiAtsu_YamameOB.jpg</v>
       </c>
       <c r="L82" t="str">
         <v/>
@@ -4044,7 +4044,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K83" t="str">
-        <v>images/daiwa_lures/Dr.ミノーII エリアチューンDr.MINNOW II AREA TUNE_DrMinnow2AreaTune_42HF_Clear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/Dr.%E3%83%9F%E3%83%8E%E3%83%BCII%20%E3%82%A8%E3%83%AA%E3%82%A2%E3%83%81%E3%83%A5%E3%83%BC%E3%83%B3Dr.MINNOW%20II%20AREA%20TUNE_DrMinnow2AreaTune_42HF_Clear.jpg</v>
       </c>
       <c r="L83" t="str">
         <v/>
@@ -4088,7 +4088,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K84" t="str">
-        <v>images/daiwa_lures/クルセイダーCRUSADER_Crusader_13S_DoPink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%AF%E3%83%AB%E3%82%BB%E3%82%A4%E3%83%80%E3%83%BCCRUSADER_Crusader_13S_DoPink.jpg</v>
       </c>
       <c r="L84" t="str">
         <v/>
@@ -4132,7 +4132,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K85" t="str">
-        <v>images/daiwa_lures/チヌーク激アツCHINOOK GEKIATSU_ChinookGekiatsu_4S_YamameOrangeBerry.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%81%E3%83%8C%E3%83%BC%E3%82%AF%E6%BF%80%E3%82%A2%E3%83%84CHINOOK%20GEKIATSU_ChinookGekiatsu_4S_YamameOrangeBerry.jpg</v>
       </c>
       <c r="L85" t="str">
         <v/>
@@ -4176,7 +4176,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K86" t="str">
-        <v>images/daiwa_lures/レーザーチヌークSLASER CHINOOK S_LazerChinookS_17S_YROrangeYamame.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%AC%E3%83%BC%E3%82%B6%E3%83%BC%E3%83%81%E3%83%8C%E3%83%BC%E3%82%AFSLASER%20CHINOOK%20S_LazerChinookS_17S_YROrangeYamame.jpg</v>
       </c>
       <c r="L86" t="str">
         <v/>
@@ -4220,7 +4220,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K87" t="str">
-        <v>images/daiwa_lures/ブレットンBRETTON_Bretton_No3_3g_G.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%96%E3%83%AC%E3%83%83%E3%83%88%E3%83%B3BRETTON_Bretton_No3_3g_G.jpg</v>
       </c>
       <c r="L87" t="str">
         <v/>
@@ -4264,7 +4264,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K88" t="str">
-        <v>images/daiwa_lures/SilverCreek スピナーSILVER CREEK SPINNER_SilverCreekSpinner_30_Mikan.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/SilverCreek%20%E3%82%B9%E3%83%94%E3%83%8A%E3%83%BCSILVER%20CREEK%20SPINNER_SilverCreekSpinner_30_Mikan.jpg</v>
       </c>
       <c r="L88" t="str">
         <v/>
@@ -4308,7 +4308,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K89" t="str">
-        <v>images/daiwa_lures/シルバークリーク スピナーSSSILVER CREEK SPINNER SS_5_CHART_YAMAME_ORANGE_BELLY_4550133494819.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20%E3%82%B9%E3%83%94%E3%83%8A%E3%83%BCSSSILVER%20CREEK%20SPINNER%20SS_5_CHART_YAMAME_ORANGE_BELLY_4550133494819.jpg</v>
       </c>
       <c r="L89" t="str">
         <v/>
@@ -4352,7 +4352,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K90" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 60F1 tuned by HMKLPRESSO DOUBLECLUTCH60F1 tuned by HMKL_PressoDoubleClutch60F1_ToppingFood.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2060F1%20tuned%20by%20HMKLPRESSO%20DOUBLECLUTCH60F1%20tuned%20by%20HMKL_PressoDoubleClutch60F1_ToppingFood.jpg</v>
       </c>
       <c r="L90" t="str">
         <v/>
@@ -4396,7 +4396,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K91" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 60SS tuned by HMKLPRESSO DOUBLE CLUTCH 60SS tuned by HMKL_PressoDoubleClutch60SSTunedByHMKL_WavePink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2060SS%20tuned%20by%20HMKLPRESSO%20DOUBLE%20CLUTCH%2060SS%20tuned%20by%20HMKL_PressoDoubleClutch60SSTunedByHMKL_WavePink.jpg</v>
       </c>
       <c r="L91" t="str">
         <v/>
@@ -4440,7 +4440,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K92" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 45S tuned by HMKLPRESSO DOUBLE CLUTCH 45S tuned by HMKL_PressoDoubleClutch45STunedHMKL_ToppingFood.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2045S%20tuned%20by%20HMKLPRESSO%20DOUBLE%20CLUTCH%2045S%20tuned%20by%20HMKL_PressoDoubleClutch45STunedHMKL_ToppingFood.jpg</v>
       </c>
       <c r="L92" t="str">
         <v/>
@@ -4484,7 +4484,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K93" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 60SHF tuned by HMKLPRESSO DOUBLECLUTCH 60SHF tuned by HMKL_Presso_DoubleClutch_60SHF_ToppingFood.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2060SHF%20tuned%20by%20HMKLPRESSO%20DOUBLECLUTCH%2060SHF%20tuned%20by%20HMKL_Presso_DoubleClutch_60SHF_ToppingFood.jpg</v>
       </c>
       <c r="L93" t="str">
         <v/>
@@ -4528,7 +4528,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K94" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 45F1 tuned by HMKLPRESSO DOUBLECLUTCH45F1 tuned by HMKL_DoubleClutch45F1_ToppingFood.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2045F1%20tuned%20by%20HMKLPRESSO%20DOUBLECLUTCH45F1%20tuned%20by%20HMKL_DoubleClutch45F1_ToppingFood.jpg</v>
       </c>
       <c r="L94" t="str">
         <v/>
@@ -4572,7 +4572,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K95" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 75SS tuned by HMKLPRESSO DOUBLE CLUTCH 75SS tuned by HMKL_PressoDoubleClutch75SSTunedByHMKL_WaveBlack.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2075SS%20tuned%20by%20HMKLPRESSO%20DOUBLE%20CLUTCH%2075SS%20tuned%20by%20HMKL_PressoDoubleClutch75SSTunedByHMKL_WaveBlack.jpg</v>
       </c>
       <c r="L95" t="str">
         <v/>
@@ -4616,7 +4616,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K96" t="str">
-        <v>images/daiwa_lures/プレッソ ワブクラJr.PRESSO WABCRA Jr.__25F_SR_GOMASHIO_GLOW_4550133555824.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%AF%E3%83%96%E3%82%AF%E3%83%A9Jr.PRESSO%20WABCRA%20Jr.__25F_SR_GOMASHIO_GLOW_4550133555824.jpg</v>
       </c>
       <c r="L96" t="str">
         <v/>
@@ -4660,7 +4660,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K97" t="str">
-        <v>images/daiwa_lures/プレッソ ワブクラスリムPRESSO WABCRA SLIM_PRESSO_WABCRA_SLIM_39F_SR_CLEAR_4550133556012.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%AF%E3%83%96%E3%82%AF%E3%83%A9%E3%82%B9%E3%83%AA%E3%83%A0PRESSO%20WABCRA%20SLIM_PRESSO_WABCRA_SLIM_39F_SR_CLEAR_4550133556012.jpg</v>
       </c>
       <c r="L97" t="str">
         <v/>
@@ -4704,7 +4704,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K98" t="str">
-        <v>images/daiwa_lures/プレッソ ダブルクラッチ 48F tuned by HMKLPRESSO DOUBLECLUTCH 48F tuned by HMKL_PRESSO_DOUBLECLUTCH_48F_TOPPING_FOOD_4550133419829.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%80%E3%83%96%E3%83%AB%E3%82%AF%E3%83%A9%E3%83%83%E3%83%81%2048F%20tuned%20by%20HMKLPRESSO%20DOUBLECLUTCH%2048F%20tuned%20by%20HMKL_PRESSO_DOUBLECLUTCH_48F_TOPPING_FOOD_4550133419829.jpg</v>
       </c>
       <c r="L98" t="str">
         <v/>
@@ -4748,7 +4748,7 @@
         <v>variable</v>
       </c>
       <c r="K99" t="str">
-        <v>images/daiwa_lures/プレッソ メガポッピンバグPRESSO MEGA POPPIN'BUG_PRESSOMEGAPOPPINBUGSAKURAHIMEGROW4550133431647.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%A1%E3%82%AC%E3%83%9D%E3%83%83%E3%83%94%E3%83%B3%E3%83%90%E3%82%B0PRESSO%20MEGA%20POPPIN'BUG_PRESSOMEGAPOPPINBUGSAKURAHIMEGROW4550133431647.jpg</v>
       </c>
       <c r="L99" t="str">
         <v/>
@@ -4792,7 +4792,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K100" t="str">
-        <v>images/daiwa_lures/プレッソ ニョロクレイジー SSSPRESSO NYORO CLAZY SSS_PRESSO_NYOROCLAZY_57SS_CLEAR_4550133657184.jpg</v>
+        <v/>
       </c>
       <c r="L100" t="str">
         <v/>
@@ -4836,7 +4836,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K101" t="str">
-        <v>images/daiwa_lures/プレッソ ステップダートPRESSO STEP DART_PressoStepDart_ReactionGold.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%B9%E3%83%86%E3%83%83%E3%83%97%E3%83%80%E3%83%BC%E3%83%88PRESSO%20STEP%20DART_PressoStepDart_ReactionGold.jpg</v>
       </c>
       <c r="L101" t="str">
         <v/>
@@ -4880,7 +4880,7 @@
         <v>variable</v>
       </c>
       <c r="K102" t="str">
-        <v>images/daiwa_lures/プレッソ ポッピンバグ  ラトリンポッピンバグPRESSO POPPIN'BUG  RATLLIN'POPPIN'BUG_PressoPoppinBug_SukeSukeBrownPellet.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%9D%E3%83%83%E3%83%94%E3%83%B3%E3%83%90%E3%82%B0%20%20%E3%83%A9%E3%83%88%E3%83%AA%E3%83%B3%E3%83%9D%E3%83%83%E3%83%94%E3%83%B3%E3%83%90%E3%82%B0PRESSO%20POPPIN'BUG%20%20RATLLIN'POPPIN'BUG_PressoPoppinBug_SukeSukeBrownPellet.jpg</v>
       </c>
       <c r="L102" t="str">
         <v/>
@@ -4924,7 +4924,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K103" t="str">
-        <v>images/daiwa_lures/プレッソ リバクラPRESSO RIVECRA_PressoRivecra30S_GomashioGrow_2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%AA%E3%83%90%E3%82%AF%E3%83%A9PRESSO%20RIVECRA_PressoRivecra30S_GomashioGrow_2.jpg</v>
       </c>
       <c r="L103" t="str">
         <v/>
@@ -4968,7 +4968,7 @@
         <v>variable</v>
       </c>
       <c r="K104" t="str">
-        <v>images/daiwa_lures/プレッソ ラトリンウェイクバグPRESSO RATLLIN'WAKE BUG_PRESSORATLLINWAKEBUG28HFCLEAR4550133656897.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%A9%E3%83%88%E3%83%AA%E3%83%B3%E3%82%A6%E3%82%A7%E3%82%A4%E3%82%AF%E3%83%90%E3%82%B0PRESSO%20RATLLIN'WAKE%20BUG_PRESSORATLLINWAKEBUG28HFCLEAR4550133656897.jpg</v>
       </c>
       <c r="L104" t="str">
         <v/>
@@ -5012,7 +5012,7 @@
         <v>jerk_dart</v>
       </c>
       <c r="K105" t="str">
-        <v>images/daiwa_lures/ドクターミノー ジョイント 5F プレッソチューンDR. MINNOW JOINT 5F PRESSO TUNE_DrMinnowJoint5FPressoTune_Clear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%89%E3%82%AF%E3%82%BF%E3%83%BC%E3%83%9F%E3%83%8E%E3%83%BC%20%E3%82%B8%E3%83%A7%E3%82%A4%E3%83%B3%E3%83%88%205F%20%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%83%81%E3%83%A5%E3%83%BC%E3%83%B3DR.%20MINNOW%20JOINT%205F%20PRESSO%20TUNE_DrMinnowJoint5FPressoTune_Clear.jpg</v>
       </c>
       <c r="L105" t="str">
         <v/>
@@ -5056,7 +5056,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K106" t="str">
-        <v>images/daiwa_lures/プレッソ ワブクラPRESSO WABCRA_PressoWabcra_DR_GomashioGlow.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%AF%E3%83%96%E3%82%AF%E3%83%A9PRESSO%20WABCRA_PressoWabcra_DR_GomashioGlow.jpg</v>
       </c>
       <c r="L106" t="str">
         <v/>
@@ -5100,7 +5100,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K107" t="str">
-        <v>images/daiwa_lures/鱒ノ芋虫MASUNO IMOMUSHI_MasunoImomushi_Clear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E8%8A%8B%E8%99%ABMASUNO%20IMOMUSHI_MasunoImomushi_Clear.jpg</v>
       </c>
       <c r="L107" t="str">
         <v/>
@@ -5144,7 +5144,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K108" t="str">
-        <v>images/daiwa_lures/プレッソ ディーザPRESSO DEAZA_PressoDeaza25_LatteGreenGrow_left.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%87%E3%82%A3%E3%83%BC%E3%82%B6PRESSO%20DEAZA_PressoDeaza25_LatteGreenGrow_left.jpg</v>
       </c>
       <c r="L108" t="str">
         <v/>
@@ -5188,7 +5188,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K109" t="str">
-        <v>images/daiwa_lures/鱒ノ小魚MASUNO KOZAKAN_MasunoKozakana_Clear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E5%B0%8F%E9%AD%9AMASUNO%20KOZAKAN_MasunoKozakana_Clear.jpg</v>
       </c>
       <c r="L109" t="str">
         <v/>
@@ -5232,7 +5232,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K110" t="str">
-        <v>images/daiwa_lures/鱒の小枝 スクリューMASU NO KOEDA SCREW_MASU_NO_KOEDA_SCREW_CLEAR_RED_4550133450167.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%81%AE%E5%B0%8F%E6%9E%9D%20%E3%82%B9%E3%82%AF%E3%83%AA%E3%83%A5%E3%83%BCMASU%20NO%20KOEDA%20SCREW_MASU_NO_KOEDA_SCREW_CLEAR_RED_4550133450167.jpg</v>
       </c>
       <c r="L110" t="str">
         <v/>
@@ -5276,7 +5276,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K111" t="str">
-        <v>images/daiwa_lures/鱒ノつぼみMASU NO TSUBOMI_MASU_NO_TSUBOMI_ANZU_4550133242960.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E3%81%A4%E3%81%BC%E3%81%BFMASU%20NO%20TSUBOMI_MASU_NO_TSUBOMI_ANZU_4550133242960.jpg</v>
       </c>
       <c r="L111" t="str">
         <v/>
@@ -5320,7 +5320,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K112" t="str">
-        <v>images/daiwa_lures/鱒ノ筒／鱒ノ筒Jr.MASU NO TSUTSU／MASU NO TSUTSU Jr._MASU_NO_TSUTSU_FLAMINGO_4550133454011.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E7%AD%92%EF%BC%8F%E9%B1%92%E3%83%8E%E7%AD%92Jr.MASU%20NO%20TSUTSU%EF%BC%8FMASU%20NO%20TSUTSU%20Jr._MASU_NO_TSUTSU_FLAMINGO_4550133454011.jpg</v>
       </c>
       <c r="L112" t="str">
         <v/>
@@ -5364,7 +5364,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K113" t="str">
-        <v>images/daiwa_lures/鱒ノ種MASUNOTANE_Masynotane_Shou10mm_Olive.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E7%A8%AEMASUNOTANE_Masynotane_Shou10mm_Olive.jpg</v>
       </c>
       <c r="L113" t="str">
         <v/>
@@ -5408,7 +5408,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K114" t="str">
-        <v>images/daiwa_lures/鱒もろこしMASUMOROKOSHI_MasuMorokoshi_SweetCorn.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%82%82%E3%82%8D%E3%81%93%E3%81%97MASUMOROKOSHI_MasuMorokoshi_SweetCorn.jpg</v>
       </c>
       <c r="L114" t="str">
         <v/>
@@ -5452,7 +5452,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K115" t="str">
-        <v>images/daiwa_lures/鱒ノ小枝／鱒ノ小枝Jr.MASUNOKOEDA／MASUNOKOEDA Jr._Masunokoeda_Mimizu.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E9%B1%92%E3%83%8E%E5%B0%8F%E6%9E%9D%EF%BC%8F%E9%B1%92%E3%83%8E%E5%B0%8F%E6%9E%9DJr.MASUNOKOEDA%EF%BC%8FMASUNOKOEDA%20Jr._Masunokoeda_Mimizu.jpg</v>
       </c>
       <c r="L115" t="str">
         <v/>
@@ -5496,7 +5496,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K116" t="str">
-        <v>images/daiwa_lures/プレッソ アトラPRESSO ATTRA_8_ORANGE_MANGO_4550133583018.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%A2%E3%83%88%E3%83%A9PRESSO%20ATTRA_8_ORANGE_MANGO_4550133583018.jpg</v>
       </c>
       <c r="L116" t="str">
         <v/>
@@ -5540,7 +5540,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K117" t="str">
-        <v>images/daiwa_lures/プレッソ イヴ激アツ 2.5PRESSO EVE GEKIATSU 2.5_PressoEveGekiatsu25_Karashi_front4550133114014.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%A4%E3%83%B4%E6%BF%80%E3%82%A2%E3%83%84%202.5PRESSO%20EVE%20GEKIATSU%202.5_PressoEveGekiatsu25_Karashi_front4550133114014.jpg</v>
       </c>
       <c r="L117" t="str">
         <v/>
@@ -5584,7 +5584,7 @@
         <v>wobble_roll</v>
       </c>
       <c r="K118" t="str">
-        <v>images/daiwa_lures/プレッソ ルミオンPRESSO LUMION_orengemango.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lures/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%83%AB%E3%83%9F%E3%82%AA%E3%83%B3PRESSO%20LUMION_orengemango.jpg</v>
       </c>
       <c r="L118" t="str">
         <v/>
